--- a/Stock_OneClick/history/scan_result_20260601_140348.xlsx
+++ b/Stock_OneClick/history/scan_result_20260601_140348.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q168"/>
+  <dimension ref="A1:Q167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -661,24 +661,6 @@
       <c r="J3" t="n">
         <v>185.67</v>
       </c>
-      <c r="K3" t="n">
-        <v/>
-      </c>
-      <c r="L3" t="n">
-        <v/>
-      </c>
-      <c r="M3" t="n">
-        <v/>
-      </c>
-      <c r="N3" t="n">
-        <v/>
-      </c>
-      <c r="O3" t="n">
-        <v/>
-      </c>
-      <c r="P3" t="n">
-        <v/>
-      </c>
       <c r="Q3" t="inlineStr">
         <is>
           <t>D0=181.49; 最新=2026-06-01; 相对D0=2.30%; 本次触发=2026-05-22(正式买入), 2026-05-27(正式买入 | 预警买入), 2026-06-01(正式买入 | 预警买入); 历史重复2次; 重复日期=2026-05-27, 2026-06-01</t>
@@ -730,24 +712,12 @@
       <c r="J4" s="5" t="n">
         <v>188.39</v>
       </c>
-      <c r="K4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P4" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+      <c r="P4" s="5" t="n"/>
       <c r="Q4" s="5" t="inlineStr">
         <is>
           <t>D0=202.91; 最新=2026-06-01; 相对D0=-7.16%; 本次触发=2026-05-22(预警买入), 2026-05-26(预警买入); 历史重复1次; 重复日期=2026-05-26</t>
@@ -799,24 +769,12 @@
       <c r="J5" s="5" t="n">
         <v>163.09</v>
       </c>
-      <c r="K5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P5" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
       <c r="Q5" s="5" t="inlineStr">
         <is>
           <t>D0=167.37; 最新=2026-06-01; 相对D0=-2.56%; 本次触发=2026-05-22(预警买入), 2026-05-26(正式买入), 2026-05-29(预警买入); 历史重复2次; 重复日期=2026-05-26, 2026-05-29</t>
@@ -868,27 +826,15 @@
       <c r="J6" s="5" t="n">
         <v>265.7</v>
       </c>
-      <c r="K6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P6" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+      <c r="P6" s="5" t="n"/>
       <c r="Q6" s="5" t="inlineStr">
         <is>
-          <t>D0=294.07; 最新=2026-06-01; 相对D0=-9.65%; 本次触发=2026-05-22(第一买入点), 2026-05-29(正式买入); 历史重复1次; 重复日期=2026-05-29</t>
+          <t>D0=294.07; 最新=2026-06-01; 相对D0=-9.65%; 本次触发=2026-05-22(第一观察点), 2026-05-29(正式买入); 历史重复1次; 重复日期=2026-05-29</t>
         </is>
       </c>
     </row>
@@ -937,24 +883,12 @@
       <c r="J7" s="5" t="n">
         <v>54.5</v>
       </c>
-      <c r="K7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P7" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+      <c r="P7" s="5" t="n"/>
       <c r="Q7" s="5" t="inlineStr">
         <is>
           <t>D0=46.53; 最新=2026-06-01; 相对D0=17.13%; 本次触发=2026-05-22(正式买入)</t>
@@ -1006,24 +940,6 @@
       <c r="J8" t="n">
         <v>16.62</v>
       </c>
-      <c r="K8" t="n">
-        <v/>
-      </c>
-      <c r="L8" t="n">
-        <v/>
-      </c>
-      <c r="M8" t="n">
-        <v/>
-      </c>
-      <c r="N8" t="n">
-        <v/>
-      </c>
-      <c r="O8" t="n">
-        <v/>
-      </c>
-      <c r="P8" t="n">
-        <v/>
-      </c>
       <c r="Q8" t="inlineStr">
         <is>
           <t>D0=16.12; 最新=2026-06-01; 相对D0=3.10%; 本次触发=2026-05-22(预警买入), 2026-05-27(正式买入 | 预警买入); 历史重复1次; 重复日期=2026-05-27</t>
@@ -1075,24 +991,12 @@
       <c r="J9" s="5" t="n">
         <v>209.6</v>
       </c>
-      <c r="K9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P9" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+      <c r="P9" s="5" t="n"/>
       <c r="Q9" s="5" t="inlineStr">
         <is>
           <t>D0=180.07; 最新=2026-06-01; 相对D0=16.40%; 本次触发=2026-05-22(正式买入 | 预警买入), 2026-05-28(预警买入), 2026-05-29(正式买入 | 预警买入); 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -1144,24 +1048,12 @@
       <c r="J10" s="5" t="n">
         <v>47.59</v>
       </c>
-      <c r="K10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P10" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
+      <c r="P10" s="5" t="n"/>
       <c r="Q10" s="5" t="inlineStr">
         <is>
           <t>D0=48.12; 最新=2026-06-01; 相对D0=-1.10%; 本次触发=2026-05-22(预警买入), 2026-05-26(正式买入), 2026-05-29(正式买入 | 预警买入); 历史重复2次; 重复日期=2026-05-26, 2026-05-29</t>
@@ -1213,24 +1105,12 @@
       <c r="J11" s="5" t="n">
         <v>135.73</v>
       </c>
-      <c r="K11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P11" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
+      <c r="P11" s="5" t="n"/>
       <c r="Q11" s="5" t="inlineStr">
         <is>
           <t>D0=135.28; 最新=2026-06-01; 相对D0=0.33%; 本次触发=2026-05-22(正式买入)</t>
@@ -1282,24 +1162,6 @@
       <c r="J12" t="n">
         <v>136.62</v>
       </c>
-      <c r="K12" t="n">
-        <v/>
-      </c>
-      <c r="L12" t="n">
-        <v/>
-      </c>
-      <c r="M12" t="n">
-        <v/>
-      </c>
-      <c r="N12" t="n">
-        <v/>
-      </c>
-      <c r="O12" t="n">
-        <v/>
-      </c>
-      <c r="P12" t="n">
-        <v/>
-      </c>
       <c r="Q12" t="inlineStr">
         <is>
           <t>D0=141.22; 最新=2026-06-01; 相对D0=-3.26%; 本次触发=2026-05-22(预警买入), 2026-06-01(预警买入); 历史重复1次; 重复日期=2026-06-01</t>
@@ -1351,24 +1213,6 @@
       <c r="J13" t="n">
         <v>400.08</v>
       </c>
-      <c r="K13" t="n">
-        <v/>
-      </c>
-      <c r="L13" t="n">
-        <v/>
-      </c>
-      <c r="M13" t="n">
-        <v/>
-      </c>
-      <c r="N13" t="n">
-        <v/>
-      </c>
-      <c r="O13" t="n">
-        <v/>
-      </c>
-      <c r="P13" t="n">
-        <v/>
-      </c>
       <c r="Q13" t="inlineStr">
         <is>
           <t>D0=391.35; 最新=2026-06-01; 相对D0=2.23%; 本次触发=2026-05-22(预警买入), 2026-05-26(正式买入); 历史重复1次; 重复日期=2026-05-26</t>
@@ -1420,24 +1264,6 @@
       <c r="J14" t="n">
         <v>50.55</v>
       </c>
-      <c r="K14" t="n">
-        <v/>
-      </c>
-      <c r="L14" t="n">
-        <v/>
-      </c>
-      <c r="M14" t="n">
-        <v/>
-      </c>
-      <c r="N14" t="n">
-        <v/>
-      </c>
-      <c r="O14" t="n">
-        <v/>
-      </c>
-      <c r="P14" t="n">
-        <v/>
-      </c>
       <c r="Q14" t="inlineStr">
         <is>
           <t>D0=50.66; 最新=2026-06-01; 相对D0=-0.22%; 本次触发=2026-05-22(正式买入 | 预警买入), 2026-05-27(正式买入 | 预警买入), 2026-06-01(正式买入 | 预警买入); 历史重复2次; 重复日期=2026-05-27, 2026-06-01</t>
@@ -1489,27 +1315,15 @@
       <c r="J15" s="5" t="n">
         <v>189</v>
       </c>
-      <c r="K15" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L15" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M15" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N15" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O15" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P15" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="5" t="n"/>
+      <c r="N15" s="5" t="n"/>
+      <c r="O15" s="5" t="n"/>
+      <c r="P15" s="5" t="n"/>
       <c r="Q15" s="5" t="inlineStr">
         <is>
-          <t>D0=179.36; 最新=2026-06-01; 相对D0=5.37%; 本次触发=2026-05-22(预警买入), 2026-05-28(正式买入 | 预警买入), 2026-06-01(正式买入 | 第一买入点 | 预警买入); 历史重复2次; 重复日期=2026-05-28, 2026-06-01</t>
+          <t>D0=179.36; 最新=2026-06-01; 相对D0=5.37%; 本次触发=2026-05-22(预警买入), 2026-05-28(正式买入 | 预警买入), 2026-06-01(正式买入 | 第一观察点 | 预警买入); 历史重复2次; 重复日期=2026-05-28, 2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1558,24 +1372,12 @@
       <c r="J16" s="5" t="n">
         <v>403.88</v>
       </c>
-      <c r="K16" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L16" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M16" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N16" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O16" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P16" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K16" s="5" t="n"/>
+      <c r="L16" s="5" t="n"/>
+      <c r="M16" s="5" t="n"/>
+      <c r="N16" s="5" t="n"/>
+      <c r="O16" s="5" t="n"/>
+      <c r="P16" s="5" t="n"/>
       <c r="Q16" s="5" t="inlineStr">
         <is>
           <t>D0=326.13; 最新=2026-06-01; 相对D0=23.84%; 本次触发=2026-05-22(预警买入), 2026-05-28(正式买入 | 预警买入), 2026-05-29(预警买入); 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -1627,24 +1429,12 @@
       <c r="J17" s="5" t="n">
         <v>600.47</v>
       </c>
-      <c r="K17" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L17" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M17" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N17" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O17" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P17" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K17" s="5" t="n"/>
+      <c r="L17" s="5" t="n"/>
+      <c r="M17" s="5" t="n"/>
+      <c r="N17" s="5" t="n"/>
+      <c r="O17" s="5" t="n"/>
+      <c r="P17" s="5" t="n"/>
       <c r="Q17" s="5" t="inlineStr">
         <is>
           <t>D0=610.26; 最新=2026-06-01; 相对D0=-1.60%; 本次触发=2026-05-22(预警买入), 2026-05-26(正式买入); 历史重复1次; 重复日期=2026-05-26</t>
@@ -1696,27 +1486,9 @@
       <c r="J18" t="n">
         <v>23.33</v>
       </c>
-      <c r="K18" t="n">
-        <v/>
-      </c>
-      <c r="L18" t="n">
-        <v/>
-      </c>
-      <c r="M18" t="n">
-        <v/>
-      </c>
-      <c r="N18" t="n">
-        <v/>
-      </c>
-      <c r="O18" t="n">
-        <v/>
-      </c>
-      <c r="P18" t="n">
-        <v/>
-      </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>D0=22.51; 最新=2026-06-01; 相对D0=3.64%; 本次触发=2026-05-22(正式买入), 2026-05-26(第一买入点); 历史重复1次; 重复日期=2026-05-26</t>
+          <t>D0=22.51; 最新=2026-06-01; 相对D0=3.64%; 本次触发=2026-05-22(正式买入), 2026-05-26(第一观察点); 历史重复1次; 重复日期=2026-05-26</t>
         </is>
       </c>
     </row>
@@ -1765,27 +1537,15 @@
       <c r="J19" s="5" t="n">
         <v>29.7</v>
       </c>
-      <c r="K19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P19" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K19" s="5" t="n"/>
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="n"/>
+      <c r="N19" s="5" t="n"/>
+      <c r="O19" s="5" t="n"/>
+      <c r="P19" s="5" t="n"/>
       <c r="Q19" s="5" t="inlineStr">
         <is>
-          <t>D0=26.73; 最新=2026-06-01; 相对D0=11.11%; 本次触发=2026-05-22(第一买入点)</t>
+          <t>D0=26.73; 最新=2026-06-01; 相对D0=11.11%; 本次触发=2026-05-22(第一观察点)</t>
         </is>
       </c>
     </row>
@@ -1834,27 +1594,9 @@
       <c r="J20" t="n">
         <v>129.47</v>
       </c>
-      <c r="K20" t="n">
-        <v/>
-      </c>
-      <c r="L20" t="n">
-        <v/>
-      </c>
-      <c r="M20" t="n">
-        <v/>
-      </c>
-      <c r="N20" t="n">
-        <v/>
-      </c>
-      <c r="O20" t="n">
-        <v/>
-      </c>
-      <c r="P20" t="n">
-        <v/>
-      </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>D0=137.65; 最新=2026-06-01; 相对D0=-5.94%; 本次触发=2026-05-22(第一买入点)</t>
+          <t>D0=137.65; 最新=2026-06-01; 相对D0=-5.94%; 本次触发=2026-05-22(第一观察点)</t>
         </is>
       </c>
     </row>
@@ -1903,24 +1645,12 @@
       <c r="J21" s="5" t="n">
         <v>251.49</v>
       </c>
-      <c r="K21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P21" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K21" s="5" t="n"/>
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="5" t="n"/>
+      <c r="O21" s="5" t="n"/>
+      <c r="P21" s="5" t="n"/>
       <c r="Q21" s="5" t="inlineStr">
         <is>
           <t>D0=232.00; 最新=2026-06-01; 相对D0=8.40%; 本次触发=2026-05-22(正式买入)</t>
@@ -1972,24 +1702,6 @@
       <c r="J22" t="n">
         <v>145.02</v>
       </c>
-      <c r="K22" t="n">
-        <v/>
-      </c>
-      <c r="L22" t="n">
-        <v/>
-      </c>
-      <c r="M22" t="n">
-        <v/>
-      </c>
-      <c r="N22" t="n">
-        <v/>
-      </c>
-      <c r="O22" t="n">
-        <v/>
-      </c>
-      <c r="P22" t="n">
-        <v/>
-      </c>
       <c r="Q22" t="inlineStr">
         <is>
           <t>D0=130.50; 最新=2026-06-01; 相对D0=11.13%; 本次触发=2026-05-22(正式买入 | 预警买入)</t>
@@ -2041,24 +1753,12 @@
       <c r="J23" s="5" t="n">
         <v>255.71</v>
       </c>
-      <c r="K23" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L23" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M23" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N23" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O23" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P23" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K23" s="5" t="n"/>
+      <c r="L23" s="5" t="n"/>
+      <c r="M23" s="5" t="n"/>
+      <c r="N23" s="5" t="n"/>
+      <c r="O23" s="5" t="n"/>
+      <c r="P23" s="5" t="n"/>
       <c r="Q23" s="5" t="inlineStr">
         <is>
           <t>D0=262.25; 最新=2026-06-01; 相对D0=-2.49%; 本次触发=2026-05-22(预警买入), 2026-05-26(正式买入 | 预警买入), 2026-05-27(预警买入); 历史重复2次; 重复日期=2026-05-26, 2026-05-27</t>
@@ -2110,24 +1810,6 @@
       <c r="J24" t="n">
         <v>58.92</v>
       </c>
-      <c r="K24" t="n">
-        <v/>
-      </c>
-      <c r="L24" t="n">
-        <v/>
-      </c>
-      <c r="M24" t="n">
-        <v/>
-      </c>
-      <c r="N24" t="n">
-        <v/>
-      </c>
-      <c r="O24" t="n">
-        <v/>
-      </c>
-      <c r="P24" t="n">
-        <v/>
-      </c>
       <c r="Q24" t="inlineStr">
         <is>
           <t>D0=58.81; 最新=2026-06-01; 相对D0=0.19%; 本次触发=2026-05-22(预警买入), 2026-06-01(正式买入 | 预警买入); 历史重复1次; 重复日期=2026-06-01</t>
@@ -2179,24 +1861,12 @@
       <c r="J25" s="5" t="n">
         <v>55.98</v>
       </c>
-      <c r="K25" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L25" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M25" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N25" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O25" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P25" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K25" s="5" t="n"/>
+      <c r="L25" s="5" t="n"/>
+      <c r="M25" s="5" t="n"/>
+      <c r="N25" s="5" t="n"/>
+      <c r="O25" s="5" t="n"/>
+      <c r="P25" s="5" t="n"/>
       <c r="Q25" s="5" t="inlineStr">
         <is>
           <t>D0=54.94; 最新=2026-06-01; 相对D0=1.89%; 本次触发=2026-05-22(预警买入), 2026-05-26(正式买入); 历史重复1次; 重复日期=2026-05-26</t>
@@ -2248,24 +1918,6 @@
       <c r="J26" t="n">
         <v>83.78</v>
       </c>
-      <c r="K26" t="n">
-        <v/>
-      </c>
-      <c r="L26" t="n">
-        <v/>
-      </c>
-      <c r="M26" t="n">
-        <v/>
-      </c>
-      <c r="N26" t="n">
-        <v/>
-      </c>
-      <c r="O26" t="n">
-        <v/>
-      </c>
-      <c r="P26" t="n">
-        <v/>
-      </c>
       <c r="Q26" t="inlineStr">
         <is>
           <t>D0=81.76; 最新=2026-06-01; 相对D0=2.47%; 本次触发=2026-05-22(预警买入), 2026-05-26(正式买入 | 预警买入); 历史重复1次; 重复日期=2026-05-26</t>
@@ -2317,27 +1969,15 @@
       <c r="J27" s="5" t="n">
         <v>115.95</v>
       </c>
-      <c r="K27" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L27" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M27" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N27" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O27" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P27" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K27" s="5" t="n"/>
+      <c r="L27" s="5" t="n"/>
+      <c r="M27" s="5" t="n"/>
+      <c r="N27" s="5" t="n"/>
+      <c r="O27" s="5" t="n"/>
+      <c r="P27" s="5" t="n"/>
       <c r="Q27" s="5" t="inlineStr">
         <is>
-          <t>D0=85.42; 最新=2026-06-01; 相对D0=35.74%; 本次触发=2026-05-22(正式买入 | 预警买入), 2026-05-27(正式买入 | 第一买入点 | 预警买入); 历史重复1次; 重复日期=2026-05-27</t>
+          <t>D0=85.42; 最新=2026-06-01; 相对D0=35.74%; 本次触发=2026-05-22(正式买入 | 预警买入), 2026-05-27(正式买入 | 第一观察点 | 预警买入); 历史重复1次; 重复日期=2026-05-27</t>
         </is>
       </c>
     </row>
@@ -2386,24 +2026,12 @@
       <c r="J28" s="5" t="n">
         <v>415.88</v>
       </c>
-      <c r="K28" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L28" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M28" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N28" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O28" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P28" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K28" s="5" t="n"/>
+      <c r="L28" s="5" t="n"/>
+      <c r="M28" s="5" t="n"/>
+      <c r="N28" s="5" t="n"/>
+      <c r="O28" s="5" t="n"/>
+      <c r="P28" s="5" t="n"/>
       <c r="Q28" s="5" t="inlineStr">
         <is>
           <t>D0=426.01; 最新=2026-06-01; 相对D0=-2.38%; 本次触发=2026-05-22(预警买入)</t>
@@ -2455,24 +2083,12 @@
       <c r="J29" s="5" t="n">
         <v>13.59</v>
       </c>
-      <c r="K29" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L29" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M29" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N29" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O29" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P29" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K29" s="5" t="n"/>
+      <c r="L29" s="5" t="n"/>
+      <c r="M29" s="5" t="n"/>
+      <c r="N29" s="5" t="n"/>
+      <c r="O29" s="5" t="n"/>
+      <c r="P29" s="5" t="n"/>
       <c r="Q29" s="5" t="inlineStr">
         <is>
           <t>D0=13.02; 最新=2026-06-01; 相对D0=4.38%; 本次触发=2026-05-22(预警买入), 2026-05-26(预警买入), 2026-05-29(正式买入); 历史重复2次; 重复日期=2026-05-26, 2026-05-29</t>
@@ -2524,24 +2140,6 @@
       <c r="J30" t="n">
         <v>379.86</v>
       </c>
-      <c r="K30" t="n">
-        <v/>
-      </c>
-      <c r="L30" t="n">
-        <v/>
-      </c>
-      <c r="M30" t="n">
-        <v/>
-      </c>
-      <c r="N30" t="n">
-        <v/>
-      </c>
-      <c r="O30" t="n">
-        <v/>
-      </c>
-      <c r="P30" t="n">
-        <v/>
-      </c>
       <c r="Q30" t="inlineStr">
         <is>
           <t>D0=388.47; 最新=2026-06-01; 相对D0=-2.22%; 本次触发=2026-05-22(正式买入 | 预警买入), 2026-05-27(预警买入); 历史重复1次; 重复日期=2026-05-27</t>
@@ -2593,27 +2191,9 @@
       <c r="J31" t="n">
         <v>154.76</v>
       </c>
-      <c r="K31" t="n">
-        <v/>
-      </c>
-      <c r="L31" t="n">
-        <v/>
-      </c>
-      <c r="M31" t="n">
-        <v/>
-      </c>
-      <c r="N31" t="n">
-        <v/>
-      </c>
-      <c r="O31" t="n">
-        <v/>
-      </c>
-      <c r="P31" t="n">
-        <v/>
-      </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>D0=156.27; 最新=2026-06-01; 相对D0=-0.97%; 本次触发=2026-05-22(第一买入点)</t>
+          <t>D0=156.27; 最新=2026-06-01; 相对D0=-0.97%; 本次触发=2026-05-22(第一观察点)</t>
         </is>
       </c>
     </row>
@@ -2662,24 +2242,12 @@
       <c r="J32" s="5" t="n">
         <v>50.92</v>
       </c>
-      <c r="K32" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L32" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M32" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N32" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O32" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P32" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K32" s="5" t="n"/>
+      <c r="L32" s="5" t="n"/>
+      <c r="M32" s="5" t="n"/>
+      <c r="N32" s="5" t="n"/>
+      <c r="O32" s="5" t="n"/>
+      <c r="P32" s="5" t="n"/>
       <c r="Q32" s="5" t="inlineStr">
         <is>
           <t>D0=50.29; 最新=2026-06-01; 相对D0=1.25%; 本次触发=2026-05-22(预警买入), 2026-05-26(正式买入); 历史重复1次; 重复日期=2026-05-26</t>
@@ -2731,24 +2299,12 @@
       <c r="J33" s="5" t="n">
         <v>72.75</v>
       </c>
-      <c r="K33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P33" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K33" s="5" t="n"/>
+      <c r="L33" s="5" t="n"/>
+      <c r="M33" s="5" t="n"/>
+      <c r="N33" s="5" t="n"/>
+      <c r="O33" s="5" t="n"/>
+      <c r="P33" s="5" t="n"/>
       <c r="Q33" s="5" t="inlineStr">
         <is>
           <t>D0=73.46; 最新=2026-06-01; 相对D0=-0.97%; 本次触发=2026-05-26(正式买入 | 预警买入), 2026-06-01(正式买入 | 预警买入); 历史重复1次; 重复日期=2026-06-01</t>
@@ -2800,24 +2356,6 @@
       <c r="J34" t="n">
         <v>459.97</v>
       </c>
-      <c r="K34" t="n">
-        <v/>
-      </c>
-      <c r="L34" t="n">
-        <v/>
-      </c>
-      <c r="M34" t="n">
-        <v/>
-      </c>
-      <c r="N34" t="n">
-        <v/>
-      </c>
-      <c r="O34" t="n">
-        <v/>
-      </c>
-      <c r="P34" t="n">
-        <v/>
-      </c>
       <c r="Q34" t="inlineStr">
         <is>
           <t>D0=422.01; 最新=2026-06-01; 相对D0=9.00%; 本次触发=2026-05-26(正式买入 | 预警买入)</t>
@@ -2869,24 +2407,12 @@
       <c r="J35" s="5" t="n">
         <v>91.22</v>
       </c>
-      <c r="K35" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L35" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M35" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N35" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O35" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P35" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K35" s="5" t="n"/>
+      <c r="L35" s="5" t="n"/>
+      <c r="M35" s="5" t="n"/>
+      <c r="N35" s="5" t="n"/>
+      <c r="O35" s="5" t="n"/>
+      <c r="P35" s="5" t="n"/>
       <c r="Q35" s="5" t="inlineStr">
         <is>
           <t>D0=86.49; 最新=2026-06-01; 相对D0=5.47%; 本次触发=2026-05-26(预警买入)</t>
@@ -2938,24 +2464,12 @@
       <c r="J36" s="5" t="n">
         <v>188.39</v>
       </c>
-      <c r="K36" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L36" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M36" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N36" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O36" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P36" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K36" s="5" t="n"/>
+      <c r="L36" s="5" t="n"/>
+      <c r="M36" s="5" t="n"/>
+      <c r="N36" s="5" t="n"/>
+      <c r="O36" s="5" t="n"/>
+      <c r="P36" s="5" t="n"/>
       <c r="Q36" s="5" t="inlineStr">
         <is>
           <t>D0=204.38; 最新=2026-06-01; 相对D0=-7.82%; 本次触发=2026-05-26(预警买入)</t>
@@ -3007,24 +2521,12 @@
       <c r="J37" s="5" t="n">
         <v>163.09</v>
       </c>
-      <c r="K37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P37" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K37" s="5" t="n"/>
+      <c r="L37" s="5" t="n"/>
+      <c r="M37" s="5" t="n"/>
+      <c r="N37" s="5" t="n"/>
+      <c r="O37" s="5" t="n"/>
+      <c r="P37" s="5" t="n"/>
       <c r="Q37" s="5" t="inlineStr">
         <is>
           <t>D0=174.73; 最新=2026-06-01; 相对D0=-6.66%; 本次触发=2026-05-26(正式买入)</t>
@@ -3076,24 +2578,12 @@
       <c r="J38" s="5" t="n">
         <v>112.59</v>
       </c>
-      <c r="K38" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L38" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M38" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N38" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O38" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P38" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K38" s="5" t="n"/>
+      <c r="L38" s="5" t="n"/>
+      <c r="M38" s="5" t="n"/>
+      <c r="N38" s="5" t="n"/>
+      <c r="O38" s="5" t="n"/>
+      <c r="P38" s="5" t="n"/>
       <c r="Q38" s="5" t="inlineStr">
         <is>
           <t>D0=108.17; 最新=2026-06-01; 相对D0=4.09%; 本次触发=2026-05-26(预警买入), 2026-05-28(正式买入); 历史重复1次; 重复日期=2026-05-28</t>
@@ -3145,24 +2635,6 @@
       <c r="J39" t="n">
         <v>124.82</v>
       </c>
-      <c r="K39" t="n">
-        <v/>
-      </c>
-      <c r="L39" t="n">
-        <v/>
-      </c>
-      <c r="M39" t="n">
-        <v/>
-      </c>
-      <c r="N39" t="n">
-        <v/>
-      </c>
-      <c r="O39" t="n">
-        <v/>
-      </c>
-      <c r="P39" t="n">
-        <v/>
-      </c>
       <c r="Q39" t="inlineStr">
         <is>
           <t>D0=105.89; 最新=2026-06-01; 相对D0=17.88%; 本次触发=2026-05-26(预警买入), 2026-05-28(预警买入), 2026-05-29(正式买入); 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -3214,24 +2686,12 @@
       <c r="J40" s="5" t="n">
         <v>47.59</v>
       </c>
-      <c r="K40" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L40" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M40" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N40" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O40" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P40" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K40" s="5" t="n"/>
+      <c r="L40" s="5" t="n"/>
+      <c r="M40" s="5" t="n"/>
+      <c r="N40" s="5" t="n"/>
+      <c r="O40" s="5" t="n"/>
+      <c r="P40" s="5" t="n"/>
       <c r="Q40" s="5" t="inlineStr">
         <is>
           <t>D0=49.46; 最新=2026-06-01; 相对D0=-3.78%; 本次触发=2026-05-26(正式买入)</t>
@@ -3283,24 +2743,6 @@
       <c r="J41" t="n">
         <v>400.08</v>
       </c>
-      <c r="K41" t="n">
-        <v/>
-      </c>
-      <c r="L41" t="n">
-        <v/>
-      </c>
-      <c r="M41" t="n">
-        <v/>
-      </c>
-      <c r="N41" t="n">
-        <v/>
-      </c>
-      <c r="O41" t="n">
-        <v/>
-      </c>
-      <c r="P41" t="n">
-        <v/>
-      </c>
       <c r="Q41" t="inlineStr">
         <is>
           <t>D0=403.13; 最新=2026-06-01; 相对D0=-0.76%; 本次触发=2026-05-26(正式买入)</t>
@@ -3352,24 +2794,6 @@
       <c r="J42" t="n">
         <v>950.54</v>
       </c>
-      <c r="K42" t="n">
-        <v/>
-      </c>
-      <c r="L42" t="n">
-        <v/>
-      </c>
-      <c r="M42" t="n">
-        <v/>
-      </c>
-      <c r="N42" t="n">
-        <v/>
-      </c>
-      <c r="O42" t="n">
-        <v/>
-      </c>
-      <c r="P42" t="n">
-        <v/>
-      </c>
       <c r="Q42" t="inlineStr">
         <is>
           <t>D0=1070.47; 最新=2026-06-01; 相对D0=-11.20%; 本次触发=2026-05-26(正式买入 | 预警买入)</t>
@@ -3421,24 +2845,12 @@
       <c r="J43" s="5" t="n">
         <v>376.37</v>
       </c>
-      <c r="K43" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L43" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M43" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N43" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O43" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P43" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K43" s="5" t="n"/>
+      <c r="L43" s="5" t="n"/>
+      <c r="M43" s="5" t="n"/>
+      <c r="N43" s="5" t="n"/>
+      <c r="O43" s="5" t="n"/>
+      <c r="P43" s="5" t="n"/>
       <c r="Q43" s="5" t="inlineStr">
         <is>
           <t>D0=388.88; 最新=2026-06-01; 相对D0=-3.22%; 本次触发=2026-05-26(正式买入 | 预警买入), 2026-05-28(正式买入); 历史重复1次; 重复日期=2026-05-28</t>
@@ -3490,24 +2902,12 @@
       <c r="J44" s="5" t="n">
         <v>69.86</v>
       </c>
-      <c r="K44" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L44" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M44" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N44" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O44" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P44" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K44" s="5" t="n"/>
+      <c r="L44" s="5" t="n"/>
+      <c r="M44" s="5" t="n"/>
+      <c r="N44" s="5" t="n"/>
+      <c r="O44" s="5" t="n"/>
+      <c r="P44" s="5" t="n"/>
       <c r="Q44" s="5" t="inlineStr">
         <is>
           <t>D0=69.63; 最新=2026-06-01; 相对D0=0.33%; 本次触发=2026-05-26(预警买入)</t>
@@ -3559,24 +2959,12 @@
       <c r="J45" s="5" t="n">
         <v>600.47</v>
       </c>
-      <c r="K45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P45" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K45" s="5" t="n"/>
+      <c r="L45" s="5" t="n"/>
+      <c r="M45" s="5" t="n"/>
+      <c r="N45" s="5" t="n"/>
+      <c r="O45" s="5" t="n"/>
+      <c r="P45" s="5" t="n"/>
       <c r="Q45" s="5" t="inlineStr">
         <is>
           <t>D0=612.34; 最新=2026-06-01; 相对D0=-1.94%; 本次触发=2026-05-26(正式买入)</t>
@@ -3628,27 +3016,9 @@
       <c r="J46" t="n">
         <v>23.33</v>
       </c>
-      <c r="K46" t="n">
-        <v/>
-      </c>
-      <c r="L46" t="n">
-        <v/>
-      </c>
-      <c r="M46" t="n">
-        <v/>
-      </c>
-      <c r="N46" t="n">
-        <v/>
-      </c>
-      <c r="O46" t="n">
-        <v/>
-      </c>
-      <c r="P46" t="n">
-        <v/>
-      </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>D0=22.62; 最新=2026-06-01; 相对D0=3.14%; 本次触发=2026-05-26(第一买入点)</t>
+          <t>D0=22.62; 最新=2026-06-01; 相对D0=3.14%; 本次触发=2026-05-26(第一观察点)</t>
         </is>
       </c>
     </row>
@@ -3697,24 +3067,12 @@
       <c r="J47" s="5" t="n">
         <v>131.85</v>
       </c>
-      <c r="K47" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L47" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M47" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N47" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O47" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P47" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K47" s="5" t="n"/>
+      <c r="L47" s="5" t="n"/>
+      <c r="M47" s="5" t="n"/>
+      <c r="N47" s="5" t="n"/>
+      <c r="O47" s="5" t="n"/>
+      <c r="P47" s="5" t="n"/>
       <c r="Q47" s="5" t="inlineStr">
         <is>
           <t>D0=134.61; 最新=2026-06-01; 相对D0=-2.05%; 本次触发=2026-05-26(正式买入), 2026-05-28(正式买入); 历史重复1次; 重复日期=2026-05-28</t>
@@ -3766,27 +3124,15 @@
       <c r="J48" s="5" t="n">
         <v>66.89</v>
       </c>
-      <c r="K48" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L48" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M48" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N48" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O48" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P48" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K48" s="5" t="n"/>
+      <c r="L48" s="5" t="n"/>
+      <c r="M48" s="5" t="n"/>
+      <c r="N48" s="5" t="n"/>
+      <c r="O48" s="5" t="n"/>
+      <c r="P48" s="5" t="n"/>
       <c r="Q48" s="5" t="inlineStr">
         <is>
-          <t>D0=68.70; 最新=2026-06-01; 相对D0=-2.63%; 本次触发=2026-05-26(第一买入点), 2026-06-01(预警买入); 历史重复1次; 重复日期=2026-06-01</t>
+          <t>D0=68.70; 最新=2026-06-01; 相对D0=-2.63%; 本次触发=2026-05-26(第一观察点), 2026-06-01(预警买入); 历史重复1次; 重复日期=2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3835,24 +3181,12 @@
       <c r="J49" s="5" t="n">
         <v>255.71</v>
       </c>
-      <c r="K49" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L49" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M49" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N49" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O49" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P49" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K49" s="5" t="n"/>
+      <c r="L49" s="5" t="n"/>
+      <c r="M49" s="5" t="n"/>
+      <c r="N49" s="5" t="n"/>
+      <c r="O49" s="5" t="n"/>
+      <c r="P49" s="5" t="n"/>
       <c r="Q49" s="5" t="inlineStr">
         <is>
           <t>D0=274.17; 最新=2026-06-01; 相对D0=-6.73%; 本次触发=2026-05-26(正式买入 | 预警买入)</t>
@@ -3904,24 +3238,12 @@
       <c r="J50" s="5" t="n">
         <v>55.98</v>
       </c>
-      <c r="K50" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L50" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M50" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N50" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O50" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P50" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K50" s="5" t="n"/>
+      <c r="L50" s="5" t="n"/>
+      <c r="M50" s="5" t="n"/>
+      <c r="N50" s="5" t="n"/>
+      <c r="O50" s="5" t="n"/>
+      <c r="P50" s="5" t="n"/>
       <c r="Q50" s="5" t="inlineStr">
         <is>
           <t>D0=56.31; 最新=2026-06-01; 相对D0=-0.59%; 本次触发=2026-05-26(正式买入)</t>
@@ -3973,24 +3295,12 @@
       <c r="J51" s="5" t="n">
         <v>108.96</v>
       </c>
-      <c r="K51" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L51" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M51" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N51" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O51" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P51" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K51" s="5" t="n"/>
+      <c r="L51" s="5" t="n"/>
+      <c r="M51" s="5" t="n"/>
+      <c r="N51" s="5" t="n"/>
+      <c r="O51" s="5" t="n"/>
+      <c r="P51" s="5" t="n"/>
       <c r="Q51" s="5" t="inlineStr">
         <is>
           <t>D0=106.94; 最新=2026-06-01; 相对D0=1.89%; 本次触发=2026-05-26(正式买入 | 预警买入)</t>
@@ -4042,27 +3352,15 @@
       <c r="J52" s="5" t="n">
         <v>12.89</v>
       </c>
-      <c r="K52" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L52" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M52" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N52" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O52" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P52" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K52" s="5" t="n"/>
+      <c r="L52" s="5" t="n"/>
+      <c r="M52" s="5" t="n"/>
+      <c r="N52" s="5" t="n"/>
+      <c r="O52" s="5" t="n"/>
+      <c r="P52" s="5" t="n"/>
       <c r="Q52" s="5" t="inlineStr">
         <is>
-          <t>D0=12.22; 最新=2026-06-01; 相对D0=5.48%; 本次触发=2026-05-26(第一买入点)</t>
+          <t>D0=12.22; 最新=2026-06-01; 相对D0=5.48%; 本次触发=2026-05-26(第一观察点)</t>
         </is>
       </c>
     </row>
@@ -4111,27 +3409,9 @@
       <c r="J53" t="n">
         <v>18.58</v>
       </c>
-      <c r="K53" t="n">
-        <v/>
-      </c>
-      <c r="L53" t="n">
-        <v/>
-      </c>
-      <c r="M53" t="n">
-        <v/>
-      </c>
-      <c r="N53" t="n">
-        <v/>
-      </c>
-      <c r="O53" t="n">
-        <v/>
-      </c>
-      <c r="P53" t="n">
-        <v/>
-      </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>D0=15.98; 最新=2026-06-01; 相对D0=16.27%; 本次触发=2026-05-26(正式买入 | 第一买入点 | 预警买入)</t>
+          <t>D0=15.98; 最新=2026-06-01; 相对D0=16.27%; 本次触发=2026-05-26(正式买入 | 第一观察点 | 预警买入)</t>
         </is>
       </c>
     </row>
@@ -4180,24 +3460,6 @@
       <c r="J54" t="n">
         <v>83.78</v>
       </c>
-      <c r="K54" t="n">
-        <v/>
-      </c>
-      <c r="L54" t="n">
-        <v/>
-      </c>
-      <c r="M54" t="n">
-        <v/>
-      </c>
-      <c r="N54" t="n">
-        <v/>
-      </c>
-      <c r="O54" t="n">
-        <v/>
-      </c>
-      <c r="P54" t="n">
-        <v/>
-      </c>
       <c r="Q54" t="inlineStr">
         <is>
           <t>D0=84.64; 最新=2026-06-01; 相对D0=-1.02%; 本次触发=2026-05-26(正式买入 | 预警买入)</t>
@@ -4249,24 +3511,12 @@
       <c r="J55" s="5" t="n">
         <v>13.59</v>
       </c>
-      <c r="K55" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L55" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M55" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N55" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O55" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P55" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K55" s="5" t="n"/>
+      <c r="L55" s="5" t="n"/>
+      <c r="M55" s="5" t="n"/>
+      <c r="N55" s="5" t="n"/>
+      <c r="O55" s="5" t="n"/>
+      <c r="P55" s="5" t="n"/>
       <c r="Q55" s="5" t="inlineStr">
         <is>
           <t>D0=13.51; 最新=2026-06-01; 相对D0=0.59%; 本次触发=2026-05-26(预警买入)</t>
@@ -4318,24 +3568,12 @@
       <c r="J56" s="5" t="n">
         <v>50.92</v>
       </c>
-      <c r="K56" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L56" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M56" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N56" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O56" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P56" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K56" s="5" t="n"/>
+      <c r="L56" s="5" t="n"/>
+      <c r="M56" s="5" t="n"/>
+      <c r="N56" s="5" t="n"/>
+      <c r="O56" s="5" t="n"/>
+      <c r="P56" s="5" t="n"/>
       <c r="Q56" s="5" t="inlineStr">
         <is>
           <t>D0=50.99; 最新=2026-06-01; 相对D0=-0.14%; 本次触发=2026-05-26(正式买入)</t>
@@ -4387,24 +3625,6 @@
       <c r="J57" t="n">
         <v>185.67</v>
       </c>
-      <c r="K57" t="n">
-        <v/>
-      </c>
-      <c r="L57" t="n">
-        <v/>
-      </c>
-      <c r="M57" t="n">
-        <v/>
-      </c>
-      <c r="N57" t="n">
-        <v/>
-      </c>
-      <c r="O57" t="n">
-        <v/>
-      </c>
-      <c r="P57" t="n">
-        <v/>
-      </c>
       <c r="Q57" t="inlineStr">
         <is>
           <t>D0=179.83; 最新=2026-06-01; 相对D0=3.25%; 本次触发=2026-05-27(正式买入 | 预警买入)</t>
@@ -4456,24 +3676,12 @@
       <c r="J58" s="5" t="n">
         <v>261.26</v>
       </c>
-      <c r="K58" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L58" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M58" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N58" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O58" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P58" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K58" s="5" t="n"/>
+      <c r="L58" s="5" t="n"/>
+      <c r="M58" s="5" t="n"/>
+      <c r="N58" s="5" t="n"/>
+      <c r="O58" s="5" t="n"/>
+      <c r="P58" s="5" t="n"/>
       <c r="Q58" s="5" t="inlineStr">
         <is>
           <t>D0=271.85; 最新=2026-06-01; 相对D0=-3.90%; 本次触发=2026-05-27(正式买入 | 预警买入)</t>
@@ -4525,24 +3733,6 @@
       <c r="J59" t="n">
         <v>16.62</v>
       </c>
-      <c r="K59" t="n">
-        <v/>
-      </c>
-      <c r="L59" t="n">
-        <v/>
-      </c>
-      <c r="M59" t="n">
-        <v/>
-      </c>
-      <c r="N59" t="n">
-        <v/>
-      </c>
-      <c r="O59" t="n">
-        <v/>
-      </c>
-      <c r="P59" t="n">
-        <v/>
-      </c>
       <c r="Q59" t="inlineStr">
         <is>
           <t>D0=16.46; 最新=2026-06-01; 相对D0=0.97%; 本次触发=2026-05-27(正式买入 | 预警买入)</t>
@@ -4594,27 +3784,9 @@
       <c r="J60" t="n">
         <v>27.76</v>
       </c>
-      <c r="K60" t="n">
-        <v/>
-      </c>
-      <c r="L60" t="n">
-        <v/>
-      </c>
-      <c r="M60" t="n">
-        <v/>
-      </c>
-      <c r="N60" t="n">
-        <v/>
-      </c>
-      <c r="O60" t="n">
-        <v/>
-      </c>
-      <c r="P60" t="n">
-        <v/>
-      </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>D0=25.20; 最新=2026-06-01; 相对D0=10.16%; 本次触发=2026-05-27(正式买入 | 第一买入点)</t>
+          <t>D0=25.20; 最新=2026-06-01; 相对D0=10.16%; 本次触发=2026-05-27(正式买入 | 第一观察点)</t>
         </is>
       </c>
     </row>
@@ -4663,24 +3835,6 @@
       <c r="J61" t="n">
         <v>90.73</v>
       </c>
-      <c r="K61" t="n">
-        <v/>
-      </c>
-      <c r="L61" t="n">
-        <v/>
-      </c>
-      <c r="M61" t="n">
-        <v/>
-      </c>
-      <c r="N61" t="n">
-        <v/>
-      </c>
-      <c r="O61" t="n">
-        <v/>
-      </c>
-      <c r="P61" t="n">
-        <v/>
-      </c>
       <c r="Q61" t="inlineStr">
         <is>
           <t>D0=76.23; 最新=2026-06-01; 相对D0=19.02%; 本次触发=2026-05-27(正式买入 | 预警买入), 2026-05-28(二进宫买入点); 历史重复1次; 重复日期=2026-05-28</t>
@@ -4732,24 +3886,6 @@
       <c r="J62" t="n">
         <v>50.55</v>
       </c>
-      <c r="K62" t="n">
-        <v/>
-      </c>
-      <c r="L62" t="n">
-        <v/>
-      </c>
-      <c r="M62" t="n">
-        <v/>
-      </c>
-      <c r="N62" t="n">
-        <v/>
-      </c>
-      <c r="O62" t="n">
-        <v/>
-      </c>
-      <c r="P62" t="n">
-        <v/>
-      </c>
       <c r="Q62" t="inlineStr">
         <is>
           <t>D0=50.44; 最新=2026-06-01; 相对D0=0.22%; 本次触发=2026-05-27(正式买入 | 预警买入)</t>
@@ -4801,24 +3937,12 @@
       <c r="J63" s="5" t="n">
         <v>135.86</v>
       </c>
-      <c r="K63" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L63" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M63" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N63" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O63" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P63" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K63" s="5" t="n"/>
+      <c r="L63" s="5" t="n"/>
+      <c r="M63" s="5" t="n"/>
+      <c r="N63" s="5" t="n"/>
+      <c r="O63" s="5" t="n"/>
+      <c r="P63" s="5" t="n"/>
       <c r="Q63" s="5" t="inlineStr">
         <is>
           <t>D0=102.12; 最新=2026-06-01; 相对D0=33.04%; 本次触发=2026-05-27(预警买入)</t>
@@ -4870,24 +3994,12 @@
       <c r="J64" s="5" t="n">
         <v>255.71</v>
       </c>
-      <c r="K64" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L64" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M64" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N64" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O64" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P64" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K64" s="5" t="n"/>
+      <c r="L64" s="5" t="n"/>
+      <c r="M64" s="5" t="n"/>
+      <c r="N64" s="5" t="n"/>
+      <c r="O64" s="5" t="n"/>
+      <c r="P64" s="5" t="n"/>
       <c r="Q64" s="5" t="inlineStr">
         <is>
           <t>D0=266.89; 最新=2026-06-01; 相对D0=-4.19%; 本次触发=2026-05-27(预警买入)</t>
@@ -4939,24 +4051,6 @@
       <c r="J65" t="n">
         <v>248.15</v>
       </c>
-      <c r="K65" t="n">
-        <v/>
-      </c>
-      <c r="L65" t="n">
-        <v/>
-      </c>
-      <c r="M65" t="n">
-        <v/>
-      </c>
-      <c r="N65" t="n">
-        <v/>
-      </c>
-      <c r="O65" t="n">
-        <v/>
-      </c>
-      <c r="P65" t="n">
-        <v/>
-      </c>
       <c r="Q65" t="inlineStr">
         <is>
           <t>D0=190.96; 最新=2026-06-01; 相对D0=29.95%; 本次触发=2026-05-27(预警买入)</t>
@@ -5008,27 +4102,15 @@
       <c r="J66" s="5" t="n">
         <v>115.95</v>
       </c>
-      <c r="K66" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L66" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M66" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N66" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O66" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P66" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K66" s="5" t="n"/>
+      <c r="L66" s="5" t="n"/>
+      <c r="M66" s="5" t="n"/>
+      <c r="N66" s="5" t="n"/>
+      <c r="O66" s="5" t="n"/>
+      <c r="P66" s="5" t="n"/>
       <c r="Q66" s="5" t="inlineStr">
         <is>
-          <t>D0=89.07; 最新=2026-06-01; 相对D0=30.18%; 本次触发=2026-05-27(正式买入 | 第一买入点 | 预警买入)</t>
+          <t>D0=89.07; 最新=2026-06-01; 相对D0=30.18%; 本次触发=2026-05-27(正式买入 | 第一观察点 | 预警买入)</t>
         </is>
       </c>
     </row>
@@ -5077,24 +4159,6 @@
       <c r="J67" t="n">
         <v>379.86</v>
       </c>
-      <c r="K67" t="n">
-        <v/>
-      </c>
-      <c r="L67" t="n">
-        <v/>
-      </c>
-      <c r="M67" t="n">
-        <v/>
-      </c>
-      <c r="N67" t="n">
-        <v/>
-      </c>
-      <c r="O67" t="n">
-        <v/>
-      </c>
-      <c r="P67" t="n">
-        <v/>
-      </c>
       <c r="Q67" t="inlineStr">
         <is>
           <t>D0=384.01; 最新=2026-06-01; 相对D0=-1.08%; 本次触发=2026-05-27(预警买入)</t>
@@ -5146,24 +4210,6 @@
       <c r="J68" t="n">
         <v>273.51</v>
       </c>
-      <c r="K68" t="n">
-        <v/>
-      </c>
-      <c r="L68" t="n">
-        <v/>
-      </c>
-      <c r="M68" t="n">
-        <v/>
-      </c>
-      <c r="N68" t="n">
-        <v/>
-      </c>
-      <c r="O68" t="n">
-        <v/>
-      </c>
-      <c r="P68" t="n">
-        <v/>
-      </c>
       <c r="Q68" t="inlineStr">
         <is>
           <t>D0=290.01; 最新=2026-06-01; 相对D0=-5.69%; 本次触发=2026-05-28(预警买入)</t>
@@ -5215,24 +4261,12 @@
       <c r="J69" s="5" t="n">
         <v>112.59</v>
       </c>
-      <c r="K69" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L69" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M69" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N69" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O69" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P69" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K69" s="5" t="n"/>
+      <c r="L69" s="5" t="n"/>
+      <c r="M69" s="5" t="n"/>
+      <c r="N69" s="5" t="n"/>
+      <c r="O69" s="5" t="n"/>
+      <c r="P69" s="5" t="n"/>
       <c r="Q69" s="5" t="inlineStr">
         <is>
           <t>D0=110.63; 最新=2026-06-01; 相对D0=1.77%; 本次触发=2026-05-28(正式买入)</t>
@@ -5284,24 +4318,6 @@
       <c r="J70" t="n">
         <v>94.15000000000001</v>
       </c>
-      <c r="K70" t="n">
-        <v/>
-      </c>
-      <c r="L70" t="n">
-        <v/>
-      </c>
-      <c r="M70" t="n">
-        <v/>
-      </c>
-      <c r="N70" t="n">
-        <v/>
-      </c>
-      <c r="O70" t="n">
-        <v/>
-      </c>
-      <c r="P70" t="n">
-        <v/>
-      </c>
       <c r="Q70" t="inlineStr">
         <is>
           <t>D0=83.68; 最新=2026-06-01; 相对D0=12.51%; 本次触发=2026-05-28(预警买入)</t>
@@ -5353,24 +4369,12 @@
       <c r="J71" s="5" t="n">
         <v>209.6</v>
       </c>
-      <c r="K71" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L71" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M71" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N71" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O71" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P71" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K71" s="5" t="n"/>
+      <c r="L71" s="5" t="n"/>
+      <c r="M71" s="5" t="n"/>
+      <c r="N71" s="5" t="n"/>
+      <c r="O71" s="5" t="n"/>
+      <c r="P71" s="5" t="n"/>
       <c r="Q71" s="5" t="inlineStr">
         <is>
           <t>D0=176.17; 最新=2026-06-01; 相对D0=18.98%; 本次触发=2026-05-28(预警买入)</t>
@@ -5422,24 +4426,6 @@
       <c r="J72" t="n">
         <v>782.17</v>
       </c>
-      <c r="K72" t="n">
-        <v/>
-      </c>
-      <c r="L72" t="n">
-        <v/>
-      </c>
-      <c r="M72" t="n">
-        <v/>
-      </c>
-      <c r="N72" t="n">
-        <v/>
-      </c>
-      <c r="O72" t="n">
-        <v/>
-      </c>
-      <c r="P72" t="n">
-        <v/>
-      </c>
       <c r="Q72" t="inlineStr">
         <is>
           <t>D0=671.00; 最新=2026-06-01; 相对D0=16.57%; 本次触发=2026-05-28(预警买入)</t>
@@ -5491,24 +4477,6 @@
       <c r="J73" t="n">
         <v>124.82</v>
       </c>
-      <c r="K73" t="n">
-        <v/>
-      </c>
-      <c r="L73" t="n">
-        <v/>
-      </c>
-      <c r="M73" t="n">
-        <v/>
-      </c>
-      <c r="N73" t="n">
-        <v/>
-      </c>
-      <c r="O73" t="n">
-        <v/>
-      </c>
-      <c r="P73" t="n">
-        <v/>
-      </c>
       <c r="Q73" t="inlineStr">
         <is>
           <t>D0=106.86; 最新=2026-06-01; 相对D0=16.81%; 本次触发=2026-05-28(预警买入)</t>
@@ -5560,24 +4528,6 @@
       <c r="J74" t="n">
         <v>64.61</v>
       </c>
-      <c r="K74" t="n">
-        <v/>
-      </c>
-      <c r="L74" t="n">
-        <v/>
-      </c>
-      <c r="M74" t="n">
-        <v/>
-      </c>
-      <c r="N74" t="n">
-        <v/>
-      </c>
-      <c r="O74" t="n">
-        <v/>
-      </c>
-      <c r="P74" t="n">
-        <v/>
-      </c>
       <c r="Q74" t="inlineStr">
         <is>
           <t>D0=67.38; 最新=2026-06-01; 相对D0=-4.11%; 本次触发=2026-05-28(预警买入)</t>
@@ -5629,24 +4579,6 @@
       <c r="J75" t="n">
         <v>147.14</v>
       </c>
-      <c r="K75" t="n">
-        <v/>
-      </c>
-      <c r="L75" t="n">
-        <v/>
-      </c>
-      <c r="M75" t="n">
-        <v/>
-      </c>
-      <c r="N75" t="n">
-        <v/>
-      </c>
-      <c r="O75" t="n">
-        <v/>
-      </c>
-      <c r="P75" t="n">
-        <v/>
-      </c>
       <c r="Q75" t="inlineStr">
         <is>
           <t>D0=129.70; 最新=2026-06-01; 相对D0=13.45%; 本次触发=2026-05-28(预警买入)</t>
@@ -5698,24 +4630,12 @@
       <c r="J76" s="5" t="n">
         <v>376.37</v>
       </c>
-      <c r="K76" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L76" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M76" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N76" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O76" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P76" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K76" s="5" t="n"/>
+      <c r="L76" s="5" t="n"/>
+      <c r="M76" s="5" t="n"/>
+      <c r="N76" s="5" t="n"/>
+      <c r="O76" s="5" t="n"/>
+      <c r="P76" s="5" t="n"/>
       <c r="Q76" s="5" t="inlineStr">
         <is>
           <t>D0=390.13; 最新=2026-06-01; 相对D0=-3.53%; 本次触发=2026-05-28(正式买入)</t>
@@ -5767,24 +4687,6 @@
       <c r="J77" t="n">
         <v>90.73</v>
       </c>
-      <c r="K77" t="n">
-        <v/>
-      </c>
-      <c r="L77" t="n">
-        <v/>
-      </c>
-      <c r="M77" t="n">
-        <v/>
-      </c>
-      <c r="N77" t="n">
-        <v/>
-      </c>
-      <c r="O77" t="n">
-        <v/>
-      </c>
-      <c r="P77" t="n">
-        <v/>
-      </c>
       <c r="Q77" t="inlineStr">
         <is>
           <t>D0=84.84; 最新=2026-06-01; 相对D0=6.94%; 本次触发=2026-05-28(二进宫买入点)</t>
@@ -5836,24 +4738,12 @@
       <c r="J78" s="5" t="n">
         <v>107.7</v>
       </c>
-      <c r="K78" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L78" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M78" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N78" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O78" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P78" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K78" s="5" t="n"/>
+      <c r="L78" s="5" t="n"/>
+      <c r="M78" s="5" t="n"/>
+      <c r="N78" s="5" t="n"/>
+      <c r="O78" s="5" t="n"/>
+      <c r="P78" s="5" t="n"/>
       <c r="Q78" s="5" t="inlineStr">
         <is>
           <t>D0=95.68; 最新=2026-06-01; 相对D0=12.56%; 本次触发=2026-05-28(预警买入)</t>
@@ -5905,24 +4795,12 @@
       <c r="J79" s="5" t="n">
         <v>189</v>
       </c>
-      <c r="K79" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L79" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M79" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N79" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O79" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P79" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K79" s="5" t="n"/>
+      <c r="L79" s="5" t="n"/>
+      <c r="M79" s="5" t="n"/>
+      <c r="N79" s="5" t="n"/>
+      <c r="O79" s="5" t="n"/>
+      <c r="P79" s="5" t="n"/>
       <c r="Q79" s="5" t="inlineStr">
         <is>
           <t>D0=185.46; 最新=2026-06-01; 相对D0=1.91%; 本次触发=2026-05-28(正式买入 | 预警买入)</t>
@@ -5974,24 +4852,12 @@
       <c r="J80" s="5" t="n">
         <v>403.88</v>
       </c>
-      <c r="K80" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L80" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M80" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N80" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O80" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P80" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K80" s="5" t="n"/>
+      <c r="L80" s="5" t="n"/>
+      <c r="M80" s="5" t="n"/>
+      <c r="N80" s="5" t="n"/>
+      <c r="O80" s="5" t="n"/>
+      <c r="P80" s="5" t="n"/>
       <c r="Q80" s="5" t="inlineStr">
         <is>
           <t>D0=325.68; 最新=2026-06-01; 相对D0=24.01%; 本次触发=2026-05-28(正式买入 | 预警买入)</t>
@@ -6043,24 +4909,12 @@
       <c r="J81" s="5" t="n">
         <v>460.52</v>
       </c>
-      <c r="K81" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L81" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M81" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N81" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O81" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P81" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K81" s="5" t="n"/>
+      <c r="L81" s="5" t="n"/>
+      <c r="M81" s="5" t="n"/>
+      <c r="N81" s="5" t="n"/>
+      <c r="O81" s="5" t="n"/>
+      <c r="P81" s="5" t="n"/>
       <c r="Q81" s="5" t="inlineStr">
         <is>
           <t>D0=426.99; 最新=2026-06-01; 相对D0=7.85%; 本次触发=2026-05-28(正式买入 | 预警买入)</t>
@@ -6112,24 +4966,6 @@
       <c r="J82" t="n">
         <v>264.51</v>
       </c>
-      <c r="K82" t="n">
-        <v/>
-      </c>
-      <c r="L82" t="n">
-        <v/>
-      </c>
-      <c r="M82" t="n">
-        <v/>
-      </c>
-      <c r="N82" t="n">
-        <v/>
-      </c>
-      <c r="O82" t="n">
-        <v/>
-      </c>
-      <c r="P82" t="n">
-        <v/>
-      </c>
       <c r="Q82" t="inlineStr">
         <is>
           <t>D0=226.34; 最新=2026-06-01; 相对D0=16.86%; 本次触发=2026-05-28(预警买入)</t>
@@ -6181,24 +5017,12 @@
       <c r="J83" s="5" t="n">
         <v>131.85</v>
       </c>
-      <c r="K83" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L83" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M83" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N83" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O83" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P83" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K83" s="5" t="n"/>
+      <c r="L83" s="5" t="n"/>
+      <c r="M83" s="5" t="n"/>
+      <c r="N83" s="5" t="n"/>
+      <c r="O83" s="5" t="n"/>
+      <c r="P83" s="5" t="n"/>
       <c r="Q83" s="5" t="inlineStr">
         <is>
           <t>D0=133.31; 最新=2026-06-01; 相对D0=-1.10%; 本次触发=2026-05-28(正式买入)</t>
@@ -6250,24 +5074,6 @@
       <c r="J84" t="n">
         <v>139.79</v>
       </c>
-      <c r="K84" t="n">
-        <v/>
-      </c>
-      <c r="L84" t="n">
-        <v/>
-      </c>
-      <c r="M84" t="n">
-        <v/>
-      </c>
-      <c r="N84" t="n">
-        <v/>
-      </c>
-      <c r="O84" t="n">
-        <v/>
-      </c>
-      <c r="P84" t="n">
-        <v/>
-      </c>
       <c r="Q84" t="inlineStr">
         <is>
           <t>D0=94.72; 最新=2026-06-01; 相对D0=47.58%; 本次触发=2026-05-28(预警买入)</t>
@@ -6319,24 +5125,6 @@
       <c r="J85" t="n">
         <v>300.48</v>
       </c>
-      <c r="K85" t="n">
-        <v/>
-      </c>
-      <c r="L85" t="n">
-        <v/>
-      </c>
-      <c r="M85" t="n">
-        <v/>
-      </c>
-      <c r="N85" t="n">
-        <v/>
-      </c>
-      <c r="O85" t="n">
-        <v/>
-      </c>
-      <c r="P85" t="n">
-        <v/>
-      </c>
       <c r="Q85" t="inlineStr">
         <is>
           <t>D0=257.77; 最新=2026-06-01; 相对D0=16.57%; 本次触发=2026-05-28(预警买入)</t>
@@ -6388,24 +5176,12 @@
       <c r="J86" s="5" t="n">
         <v>160.65</v>
       </c>
-      <c r="K86" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L86" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M86" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N86" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O86" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P86" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K86" s="5" t="n"/>
+      <c r="L86" s="5" t="n"/>
+      <c r="M86" s="5" t="n"/>
+      <c r="N86" s="5" t="n"/>
+      <c r="O86" s="5" t="n"/>
+      <c r="P86" s="5" t="n"/>
       <c r="Q86" s="5" t="inlineStr">
         <is>
           <t>D0=143.34; 最新=2026-06-01; 相对D0=12.08%; 本次触发=2026-05-28(二进宫买入点 | 正式买入 | 预警买入)</t>
@@ -6457,27 +5233,15 @@
       <c r="J87" s="5" t="n">
         <v>274.03</v>
       </c>
-      <c r="K87" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L87" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M87" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N87" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O87" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P87" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K87" s="5" t="n"/>
+      <c r="L87" s="5" t="n"/>
+      <c r="M87" s="5" t="n"/>
+      <c r="N87" s="5" t="n"/>
+      <c r="O87" s="5" t="n"/>
+      <c r="P87" s="5" t="n"/>
       <c r="Q87" s="5" t="inlineStr">
         <is>
-          <t>D0=259.21; 最新=2026-06-01; 相对D0=5.72%; 本次触发=2026-05-29(正式买入 | 第一买入点 | 预警买入)</t>
+          <t>D0=259.21; 最新=2026-06-01; 相对D0=5.72%; 本次触发=2026-05-29(正式买入 | 第一观察点 | 预警买入)</t>
         </is>
       </c>
     </row>
@@ -6526,24 +5290,12 @@
       <c r="J88" s="5" t="n">
         <v>163.09</v>
       </c>
-      <c r="K88" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L88" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M88" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N88" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O88" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P88" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K88" s="5" t="n"/>
+      <c r="L88" s="5" t="n"/>
+      <c r="M88" s="5" t="n"/>
+      <c r="N88" s="5" t="n"/>
+      <c r="O88" s="5" t="n"/>
+      <c r="P88" s="5" t="n"/>
       <c r="Q88" s="5" t="inlineStr">
         <is>
           <t>D0=171.66; 最新=2026-06-01; 相对D0=-4.99%; 本次触发=2026-05-29(预警买入)</t>
@@ -6595,24 +5347,12 @@
       <c r="J89" s="5" t="n">
         <v>265.7</v>
       </c>
-      <c r="K89" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L89" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M89" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N89" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O89" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P89" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K89" s="5" t="n"/>
+      <c r="L89" s="5" t="n"/>
+      <c r="M89" s="5" t="n"/>
+      <c r="N89" s="5" t="n"/>
+      <c r="O89" s="5" t="n"/>
+      <c r="P89" s="5" t="n"/>
       <c r="Q89" s="5" t="inlineStr">
         <is>
           <t>D0=287.75; 最新=2026-06-01; 相对D0=-7.66%; 本次触发=2026-05-29(正式买入)</t>
@@ -6664,24 +5404,6 @@
       <c r="J90" t="n">
         <v>182.61</v>
       </c>
-      <c r="K90" t="n">
-        <v/>
-      </c>
-      <c r="L90" t="n">
-        <v/>
-      </c>
-      <c r="M90" t="n">
-        <v/>
-      </c>
-      <c r="N90" t="n">
-        <v/>
-      </c>
-      <c r="O90" t="n">
-        <v/>
-      </c>
-      <c r="P90" t="n">
-        <v/>
-      </c>
       <c r="Q90" t="inlineStr">
         <is>
           <t>D0=189.03; 最新=2026-06-01; 相对D0=-3.40%; 本次触发=2026-05-29(正式买入 | 预警买入)</t>
@@ -6733,24 +5455,12 @@
       <c r="J91" s="5" t="n">
         <v>209.6</v>
       </c>
-      <c r="K91" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L91" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M91" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N91" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O91" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P91" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K91" s="5" t="n"/>
+      <c r="L91" s="5" t="n"/>
+      <c r="M91" s="5" t="n"/>
+      <c r="N91" s="5" t="n"/>
+      <c r="O91" s="5" t="n"/>
+      <c r="P91" s="5" t="n"/>
       <c r="Q91" s="5" t="inlineStr">
         <is>
           <t>D0=191.10; 最新=2026-06-01; 相对D0=9.68%; 本次触发=2026-05-29(正式买入 | 预警买入)</t>
@@ -6802,24 +5512,6 @@
       <c r="J92" t="n">
         <v>124.82</v>
       </c>
-      <c r="K92" t="n">
-        <v/>
-      </c>
-      <c r="L92" t="n">
-        <v/>
-      </c>
-      <c r="M92" t="n">
-        <v/>
-      </c>
-      <c r="N92" t="n">
-        <v/>
-      </c>
-      <c r="O92" t="n">
-        <v/>
-      </c>
-      <c r="P92" t="n">
-        <v/>
-      </c>
       <c r="Q92" t="inlineStr">
         <is>
           <t>D0=109.53; 最新=2026-06-01; 相对D0=13.96%; 本次触发=2026-05-29(正式买入)</t>
@@ -6871,24 +5563,12 @@
       <c r="J93" s="5" t="n">
         <v>47.59</v>
       </c>
-      <c r="K93" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L93" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M93" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N93" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O93" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P93" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K93" s="5" t="n"/>
+      <c r="L93" s="5" t="n"/>
+      <c r="M93" s="5" t="n"/>
+      <c r="N93" s="5" t="n"/>
+      <c r="O93" s="5" t="n"/>
+      <c r="P93" s="5" t="n"/>
       <c r="Q93" s="5" t="inlineStr">
         <is>
           <t>D0=48.42; 最新=2026-06-01; 相对D0=-1.71%; 本次触发=2026-05-29(正式买入 | 预警买入)</t>
@@ -6940,24 +5620,6 @@
       <c r="J94" t="n">
         <v>1940.04</v>
       </c>
-      <c r="K94" t="n">
-        <v/>
-      </c>
-      <c r="L94" t="n">
-        <v/>
-      </c>
-      <c r="M94" t="n">
-        <v/>
-      </c>
-      <c r="N94" t="n">
-        <v/>
-      </c>
-      <c r="O94" t="n">
-        <v/>
-      </c>
-      <c r="P94" t="n">
-        <v/>
-      </c>
       <c r="Q94" t="inlineStr">
         <is>
           <t>D0=1921.71; 最新=2026-06-01; 相对D0=0.95%; 本次触发=2026-05-29(预警买入)</t>
@@ -7009,24 +5671,12 @@
       <c r="J95" s="5" t="n">
         <v>403.88</v>
       </c>
-      <c r="K95" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L95" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M95" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N95" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O95" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P95" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K95" s="5" t="n"/>
+      <c r="L95" s="5" t="n"/>
+      <c r="M95" s="5" t="n"/>
+      <c r="N95" s="5" t="n"/>
+      <c r="O95" s="5" t="n"/>
+      <c r="P95" s="5" t="n"/>
       <c r="Q95" s="5" t="inlineStr">
         <is>
           <t>D0=335.55; 最新=2026-06-01; 相对D0=20.36%; 本次触发=2026-05-29(预警买入)</t>
@@ -7078,24 +5728,12 @@
       <c r="J96" s="5" t="n">
         <v>224.36</v>
       </c>
-      <c r="K96" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L96" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M96" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N96" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O96" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P96" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K96" s="5" t="n"/>
+      <c r="L96" s="5" t="n"/>
+      <c r="M96" s="5" t="n"/>
+      <c r="N96" s="5" t="n"/>
+      <c r="O96" s="5" t="n"/>
+      <c r="P96" s="5" t="n"/>
       <c r="Q96" s="5" t="inlineStr">
         <is>
           <t>D0=211.14; 最新=2026-06-01; 相对D0=6.26%; 本次触发=2026-05-29(预警买入), 2026-06-01(正式买入 | 预警买入); 历史重复1次; 重复日期=2026-06-01</t>
@@ -7147,24 +5785,12 @@
       <c r="J97" s="5" t="n">
         <v>369.47</v>
       </c>
-      <c r="K97" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L97" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M97" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N97" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O97" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P97" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K97" s="5" t="n"/>
+      <c r="L97" s="5" t="n"/>
+      <c r="M97" s="5" t="n"/>
+      <c r="N97" s="5" t="n"/>
+      <c r="O97" s="5" t="n"/>
+      <c r="P97" s="5" t="n"/>
       <c r="Q97" s="5" t="inlineStr">
         <is>
           <t>D0=374.31; 最新=2026-06-01; 相对D0=-1.29%; 本次触发=2026-05-29(预警买入)</t>
@@ -7216,24 +5842,12 @@
       <c r="J98" s="5" t="n">
         <v>13.59</v>
       </c>
-      <c r="K98" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L98" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M98" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N98" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O98" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P98" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K98" s="5" t="n"/>
+      <c r="L98" s="5" t="n"/>
+      <c r="M98" s="5" t="n"/>
+      <c r="N98" s="5" t="n"/>
+      <c r="O98" s="5" t="n"/>
+      <c r="P98" s="5" t="n"/>
       <c r="Q98" s="5" t="inlineStr">
         <is>
           <t>D0=13.77; 最新=2026-06-01; 相对D0=-1.31%; 本次触发=2026-05-29(正式买入)</t>
@@ -7285,24 +5899,6 @@
       <c r="J99" t="n">
         <v>51.43</v>
       </c>
-      <c r="K99" t="n">
-        <v/>
-      </c>
-      <c r="L99" t="n">
-        <v/>
-      </c>
-      <c r="M99" t="n">
-        <v/>
-      </c>
-      <c r="N99" t="n">
-        <v/>
-      </c>
-      <c r="O99" t="n">
-        <v/>
-      </c>
-      <c r="P99" t="n">
-        <v/>
-      </c>
       <c r="Q99" t="inlineStr">
         <is>
           <t>D0=51.58; 最新=2026-06-01; 相对D0=-0.29%; 本次触发=2026-05-29(正式买入 | 预警买入)</t>
@@ -7354,24 +5950,6 @@
       <c r="J100" t="n">
         <v>185.67</v>
       </c>
-      <c r="K100" t="n">
-        <v/>
-      </c>
-      <c r="L100" t="n">
-        <v/>
-      </c>
-      <c r="M100" t="n">
-        <v/>
-      </c>
-      <c r="N100" t="n">
-        <v/>
-      </c>
-      <c r="O100" t="n">
-        <v/>
-      </c>
-      <c r="P100" t="n">
-        <v/>
-      </c>
       <c r="Q100" t="inlineStr">
         <is>
           <t>D0=185.67; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -7423,24 +6001,6 @@
       <c r="J101" t="n">
         <v>14.7</v>
       </c>
-      <c r="K101" t="n">
-        <v/>
-      </c>
-      <c r="L101" t="n">
-        <v/>
-      </c>
-      <c r="M101" t="n">
-        <v/>
-      </c>
-      <c r="N101" t="n">
-        <v/>
-      </c>
-      <c r="O101" t="n">
-        <v/>
-      </c>
-      <c r="P101" t="n">
-        <v/>
-      </c>
       <c r="Q101" t="inlineStr">
         <is>
           <t>D0=14.70; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -7492,24 +6052,12 @@
       <c r="J102" s="5" t="n">
         <v>72.75</v>
       </c>
-      <c r="K102" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L102" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M102" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N102" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O102" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P102" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K102" s="5" t="n"/>
+      <c r="L102" s="5" t="n"/>
+      <c r="M102" s="5" t="n"/>
+      <c r="N102" s="5" t="n"/>
+      <c r="O102" s="5" t="n"/>
+      <c r="P102" s="5" t="n"/>
       <c r="Q102" s="5" t="inlineStr">
         <is>
           <t>D0=72.75; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -7561,24 +6109,6 @@
       <c r="J103" t="n">
         <v>320.41</v>
       </c>
-      <c r="K103" t="n">
-        <v/>
-      </c>
-      <c r="L103" t="n">
-        <v/>
-      </c>
-      <c r="M103" t="n">
-        <v/>
-      </c>
-      <c r="N103" t="n">
-        <v/>
-      </c>
-      <c r="O103" t="n">
-        <v/>
-      </c>
-      <c r="P103" t="n">
-        <v/>
-      </c>
       <c r="Q103" t="inlineStr">
         <is>
           <t>D0=320.41; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -7630,24 +6160,6 @@
       <c r="J104" t="n">
         <v>185.83</v>
       </c>
-      <c r="K104" t="n">
-        <v/>
-      </c>
-      <c r="L104" t="n">
-        <v/>
-      </c>
-      <c r="M104" t="n">
-        <v/>
-      </c>
-      <c r="N104" t="n">
-        <v/>
-      </c>
-      <c r="O104" t="n">
-        <v/>
-      </c>
-      <c r="P104" t="n">
-        <v/>
-      </c>
       <c r="Q104" t="inlineStr">
         <is>
           <t>D0=185.83; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -7699,24 +6211,6 @@
       <c r="J105" t="n">
         <v>136.62</v>
       </c>
-      <c r="K105" t="n">
-        <v/>
-      </c>
-      <c r="L105" t="n">
-        <v/>
-      </c>
-      <c r="M105" t="n">
-        <v/>
-      </c>
-      <c r="N105" t="n">
-        <v/>
-      </c>
-      <c r="O105" t="n">
-        <v/>
-      </c>
-      <c r="P105" t="n">
-        <v/>
-      </c>
       <c r="Q105" t="inlineStr">
         <is>
           <t>D0=136.62; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -7768,24 +6262,6 @@
       <c r="J106" t="n">
         <v>8.970000000000001</v>
       </c>
-      <c r="K106" t="n">
-        <v/>
-      </c>
-      <c r="L106" t="n">
-        <v/>
-      </c>
-      <c r="M106" t="n">
-        <v/>
-      </c>
-      <c r="N106" t="n">
-        <v/>
-      </c>
-      <c r="O106" t="n">
-        <v/>
-      </c>
-      <c r="P106" t="n">
-        <v/>
-      </c>
       <c r="Q106" t="inlineStr">
         <is>
           <t>D0=8.97; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -7837,24 +6313,6 @@
       <c r="J107" t="n">
         <v>27.15</v>
       </c>
-      <c r="K107" t="n">
-        <v/>
-      </c>
-      <c r="L107" t="n">
-        <v/>
-      </c>
-      <c r="M107" t="n">
-        <v/>
-      </c>
-      <c r="N107" t="n">
-        <v/>
-      </c>
-      <c r="O107" t="n">
-        <v/>
-      </c>
-      <c r="P107" t="n">
-        <v/>
-      </c>
       <c r="Q107" t="inlineStr">
         <is>
           <t>D0=27.15; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -7906,24 +6364,6 @@
       <c r="J108" t="n">
         <v>50.55</v>
       </c>
-      <c r="K108" t="n">
-        <v/>
-      </c>
-      <c r="L108" t="n">
-        <v/>
-      </c>
-      <c r="M108" t="n">
-        <v/>
-      </c>
-      <c r="N108" t="n">
-        <v/>
-      </c>
-      <c r="O108" t="n">
-        <v/>
-      </c>
-      <c r="P108" t="n">
-        <v/>
-      </c>
       <c r="Q108" t="inlineStr">
         <is>
           <t>D0=50.55; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -7975,27 +6415,15 @@
       <c r="J109" s="5" t="n">
         <v>189</v>
       </c>
-      <c r="K109" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L109" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M109" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N109" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O109" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P109" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K109" s="5" t="n"/>
+      <c r="L109" s="5" t="n"/>
+      <c r="M109" s="5" t="n"/>
+      <c r="N109" s="5" t="n"/>
+      <c r="O109" s="5" t="n"/>
+      <c r="P109" s="5" t="n"/>
       <c r="Q109" s="5" t="inlineStr">
         <is>
-          <t>D0=189.00; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 第一买入点 | 预警买入)</t>
+          <t>D0=189.00; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 第一观察点 | 预警买入)</t>
         </is>
       </c>
     </row>
@@ -8044,24 +6472,6 @@
       <c r="J110" t="n">
         <v>905</v>
       </c>
-      <c r="K110" t="n">
-        <v/>
-      </c>
-      <c r="L110" t="n">
-        <v/>
-      </c>
-      <c r="M110" t="n">
-        <v/>
-      </c>
-      <c r="N110" t="n">
-        <v/>
-      </c>
-      <c r="O110" t="n">
-        <v/>
-      </c>
-      <c r="P110" t="n">
-        <v/>
-      </c>
       <c r="Q110" t="inlineStr">
         <is>
           <t>D0=905.00; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -8113,24 +6523,6 @@
       <c r="J111" t="n">
         <v>11.02</v>
       </c>
-      <c r="K111" t="n">
-        <v/>
-      </c>
-      <c r="L111" t="n">
-        <v/>
-      </c>
-      <c r="M111" t="n">
-        <v/>
-      </c>
-      <c r="N111" t="n">
-        <v/>
-      </c>
-      <c r="O111" t="n">
-        <v/>
-      </c>
-      <c r="P111" t="n">
-        <v/>
-      </c>
       <c r="Q111" t="inlineStr">
         <is>
           <t>D0=11.02; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -8182,24 +6574,6 @@
       <c r="J112" t="n">
         <v>69.56999999999999</v>
       </c>
-      <c r="K112" t="n">
-        <v/>
-      </c>
-      <c r="L112" t="n">
-        <v/>
-      </c>
-      <c r="M112" t="n">
-        <v/>
-      </c>
-      <c r="N112" t="n">
-        <v/>
-      </c>
-      <c r="O112" t="n">
-        <v/>
-      </c>
-      <c r="P112" t="n">
-        <v/>
-      </c>
       <c r="Q112" t="inlineStr">
         <is>
           <t>D0=69.57; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -8251,24 +6625,12 @@
       <c r="J113" s="5" t="n">
         <v>224.36</v>
       </c>
-      <c r="K113" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L113" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M113" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N113" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O113" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P113" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K113" s="5" t="n"/>
+      <c r="L113" s="5" t="n"/>
+      <c r="M113" s="5" t="n"/>
+      <c r="N113" s="5" t="n"/>
+      <c r="O113" s="5" t="n"/>
+      <c r="P113" s="5" t="n"/>
       <c r="Q113" s="5" t="inlineStr">
         <is>
           <t>D0=224.36; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -8320,24 +6682,12 @@
       <c r="J114" s="5" t="n">
         <v>66.89</v>
       </c>
-      <c r="K114" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L114" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M114" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N114" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O114" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P114" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K114" s="5" t="n"/>
+      <c r="L114" s="5" t="n"/>
+      <c r="M114" s="5" t="n"/>
+      <c r="N114" s="5" t="n"/>
+      <c r="O114" s="5" t="n"/>
+      <c r="P114" s="5" t="n"/>
       <c r="Q114" s="5" t="inlineStr">
         <is>
           <t>D0=66.89; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -8389,24 +6739,6 @@
       <c r="J115" t="n">
         <v>58.92</v>
       </c>
-      <c r="K115" t="n">
-        <v/>
-      </c>
-      <c r="L115" t="n">
-        <v/>
-      </c>
-      <c r="M115" t="n">
-        <v/>
-      </c>
-      <c r="N115" t="n">
-        <v/>
-      </c>
-      <c r="O115" t="n">
-        <v/>
-      </c>
-      <c r="P115" t="n">
-        <v/>
-      </c>
       <c r="Q115" t="inlineStr">
         <is>
           <t>D0=58.92; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -8458,24 +6790,6 @@
       <c r="J116" t="n">
         <v>13.89</v>
       </c>
-      <c r="K116" t="n">
-        <v/>
-      </c>
-      <c r="L116" t="n">
-        <v/>
-      </c>
-      <c r="M116" t="n">
-        <v/>
-      </c>
-      <c r="N116" t="n">
-        <v/>
-      </c>
-      <c r="O116" t="n">
-        <v/>
-      </c>
-      <c r="P116" t="n">
-        <v/>
-      </c>
       <c r="Q116" t="inlineStr">
         <is>
           <t>D0=13.89; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -8527,24 +6841,6 @@
       <c r="J117" t="n">
         <v>15.58</v>
       </c>
-      <c r="K117" t="n">
-        <v/>
-      </c>
-      <c r="L117" t="n">
-        <v/>
-      </c>
-      <c r="M117" t="n">
-        <v/>
-      </c>
-      <c r="N117" t="n">
-        <v/>
-      </c>
-      <c r="O117" t="n">
-        <v/>
-      </c>
-      <c r="P117" t="n">
-        <v/>
-      </c>
       <c r="Q117" t="inlineStr">
         <is>
           <t>D0=15.58; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -8596,24 +6892,12 @@
       <c r="J118" s="5" t="n">
         <v>17.62</v>
       </c>
-      <c r="K118" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L118" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M118" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N118" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O118" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P118" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K118" s="5" t="n"/>
+      <c r="L118" s="5" t="n"/>
+      <c r="M118" s="5" t="n"/>
+      <c r="N118" s="5" t="n"/>
+      <c r="O118" s="5" t="n"/>
+      <c r="P118" s="5" t="n"/>
       <c r="Q118" s="5" t="inlineStr">
         <is>
           <t>D0=17.62; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -8665,24 +6949,6 @@
       <c r="J119" t="n">
         <v>323.39</v>
       </c>
-      <c r="K119" t="n">
-        <v/>
-      </c>
-      <c r="L119" t="n">
-        <v/>
-      </c>
-      <c r="M119" t="n">
-        <v/>
-      </c>
-      <c r="N119" t="n">
-        <v/>
-      </c>
-      <c r="O119" t="n">
-        <v/>
-      </c>
-      <c r="P119" t="n">
-        <v/>
-      </c>
       <c r="Q119" t="inlineStr">
         <is>
           <t>D0=323.39; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -8733,24 +6999,6 @@
       </c>
       <c r="J120" t="n">
         <v>155.71</v>
-      </c>
-      <c r="K120" t="n">
-        <v/>
-      </c>
-      <c r="L120" t="n">
-        <v/>
-      </c>
-      <c r="M120" t="n">
-        <v/>
-      </c>
-      <c r="N120" t="n">
-        <v/>
-      </c>
-      <c r="O120" t="n">
-        <v/>
-      </c>
-      <c r="P120" t="n">
-        <v/>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -8988,24 +7236,12 @@
       <c r="J132" s="5" t="n">
         <v>39.35</v>
       </c>
-      <c r="K132" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L132" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M132" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N132" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O132" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P132" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K132" s="5" t="n"/>
+      <c r="L132" s="5" t="n"/>
+      <c r="M132" s="5" t="n"/>
+      <c r="N132" s="5" t="n"/>
+      <c r="O132" s="5" t="n"/>
+      <c r="P132" s="5" t="n"/>
       <c r="Q132" s="5" t="inlineStr">
         <is>
           <t>D0=41.47; 最新=2026-06-01; 相对D0=-5.11%; 本次触发=2026-05-22(正式卖出)</t>
@@ -9057,24 +7293,12 @@
       <c r="J133" s="5" t="n">
         <v>185.83</v>
       </c>
-      <c r="K133" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L133" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M133" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N133" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O133" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P133" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K133" s="5" t="n"/>
+      <c r="L133" s="5" t="n"/>
+      <c r="M133" s="5" t="n"/>
+      <c r="N133" s="5" t="n"/>
+      <c r="O133" s="5" t="n"/>
+      <c r="P133" s="5" t="n"/>
       <c r="Q133" s="5" t="inlineStr">
         <is>
           <t>D0=184.71; 最新=2026-06-01; 相对D0=0.61%; 本次触发=2026-05-26(正式卖出)</t>
@@ -9126,24 +7350,12 @@
       <c r="J134" s="5" t="n">
         <v>136.62</v>
       </c>
-      <c r="K134" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L134" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M134" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N134" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O134" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P134" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K134" s="5" t="n"/>
+      <c r="L134" s="5" t="n"/>
+      <c r="M134" s="5" t="n"/>
+      <c r="N134" s="5" t="n"/>
+      <c r="O134" s="5" t="n"/>
+      <c r="P134" s="5" t="n"/>
       <c r="Q134" s="5" t="inlineStr">
         <is>
           <t>D0=136.20; 最新=2026-06-01; 相对D0=0.31%; 本次触发=2026-05-26(正式卖出)</t>
@@ -9195,24 +7407,6 @@
       <c r="J135" t="n">
         <v>403.88</v>
       </c>
-      <c r="K135" t="n">
-        <v/>
-      </c>
-      <c r="L135" t="n">
-        <v/>
-      </c>
-      <c r="M135" t="n">
-        <v/>
-      </c>
-      <c r="N135" t="n">
-        <v/>
-      </c>
-      <c r="O135" t="n">
-        <v/>
-      </c>
-      <c r="P135" t="n">
-        <v/>
-      </c>
       <c r="Q135" t="inlineStr">
         <is>
           <t>D0=307.35; 最新=2026-06-01; 相对D0=31.41%; 本次触发=2026-05-26(正式卖出)</t>
@@ -9264,24 +7458,12 @@
       <c r="J136" s="5" t="n">
         <v>58.92</v>
       </c>
-      <c r="K136" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L136" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M136" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N136" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O136" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P136" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K136" s="5" t="n"/>
+      <c r="L136" s="5" t="n"/>
+      <c r="M136" s="5" t="n"/>
+      <c r="N136" s="5" t="n"/>
+      <c r="O136" s="5" t="n"/>
+      <c r="P136" s="5" t="n"/>
       <c r="Q136" s="5" t="inlineStr">
         <is>
           <t>D0=57.46; 最新=2026-06-01; 相对D0=2.54%; 本次触发=2026-05-26(正式卖出)</t>
@@ -9333,24 +7515,12 @@
       <c r="J137" s="5" t="n">
         <v>13.89</v>
       </c>
-      <c r="K137" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L137" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M137" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N137" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O137" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P137" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K137" s="5" t="n"/>
+      <c r="L137" s="5" t="n"/>
+      <c r="M137" s="5" t="n"/>
+      <c r="N137" s="5" t="n"/>
+      <c r="O137" s="5" t="n"/>
+      <c r="P137" s="5" t="n"/>
       <c r="Q137" s="5" t="inlineStr">
         <is>
           <t>D0=13.35; 最新=2026-06-01; 相对D0=4.04%; 本次触发=2026-05-26(正式卖出)</t>
@@ -9402,24 +7572,12 @@
       <c r="J138" s="5" t="n">
         <v>57.3</v>
       </c>
-      <c r="K138" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L138" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M138" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N138" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O138" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P138" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K138" s="5" t="n"/>
+      <c r="L138" s="5" t="n"/>
+      <c r="M138" s="5" t="n"/>
+      <c r="N138" s="5" t="n"/>
+      <c r="O138" s="5" t="n"/>
+      <c r="P138" s="5" t="n"/>
       <c r="Q138" s="5" t="inlineStr">
         <is>
           <t>D0=57.85; 最新=2026-06-01; 相对D0=-0.95%; 本次触发=2026-05-26(正式卖出)</t>
@@ -9471,24 +7629,12 @@
       <c r="J139" s="5" t="n">
         <v>54.75</v>
       </c>
-      <c r="K139" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L139" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M139" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N139" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O139" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P139" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K139" s="5" t="n"/>
+      <c r="L139" s="5" t="n"/>
+      <c r="M139" s="5" t="n"/>
+      <c r="N139" s="5" t="n"/>
+      <c r="O139" s="5" t="n"/>
+      <c r="P139" s="5" t="n"/>
       <c r="Q139" s="5" t="inlineStr">
         <is>
           <t>D0=56.50; 最新=2026-06-01; 相对D0=-3.10%; 本次触发=2026-05-27(正式卖出 | 预警卖出)</t>
@@ -9540,24 +7686,6 @@
       <c r="J140" t="n">
         <v>155.71</v>
       </c>
-      <c r="K140" t="n">
-        <v/>
-      </c>
-      <c r="L140" t="n">
-        <v/>
-      </c>
-      <c r="M140" t="n">
-        <v/>
-      </c>
-      <c r="N140" t="n">
-        <v/>
-      </c>
-      <c r="O140" t="n">
-        <v/>
-      </c>
-      <c r="P140" t="n">
-        <v/>
-      </c>
       <c r="Q140" t="inlineStr">
         <is>
           <t>D0=126.41; 最新=2026-06-01; 相对D0=23.18%; 本次触发=2026-05-27(正式卖出 | 预警卖出)</t>
@@ -9609,24 +7737,12 @@
       <c r="J141" s="5" t="n">
         <v>109.55</v>
       </c>
-      <c r="K141" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L141" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M141" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N141" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O141" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P141" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K141" s="5" t="n"/>
+      <c r="L141" s="5" t="n"/>
+      <c r="M141" s="5" t="n"/>
+      <c r="N141" s="5" t="n"/>
+      <c r="O141" s="5" t="n"/>
+      <c r="P141" s="5" t="n"/>
       <c r="Q141" s="5" t="inlineStr">
         <is>
           <t>D0=115.70; 最新=2026-06-01; 相对D0=-5.32%; 本次触发=2026-05-28(正式卖出)</t>
@@ -9678,24 +7794,6 @@
       <c r="J142" t="n">
         <v>265.7</v>
       </c>
-      <c r="K142" t="n">
-        <v/>
-      </c>
-      <c r="L142" t="n">
-        <v/>
-      </c>
-      <c r="M142" t="n">
-        <v/>
-      </c>
-      <c r="N142" t="n">
-        <v/>
-      </c>
-      <c r="O142" t="n">
-        <v/>
-      </c>
-      <c r="P142" t="n">
-        <v/>
-      </c>
       <c r="Q142" t="inlineStr">
         <is>
           <t>D0=286.31; 最新=2026-06-01; 相对D0=-7.20%; 本次触发=2026-05-28(正式卖出)</t>
@@ -9747,24 +7845,12 @@
       <c r="J143" s="5" t="n">
         <v>176.7</v>
       </c>
-      <c r="K143" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L143" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M143" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N143" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O143" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P143" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K143" s="5" t="n"/>
+      <c r="L143" s="5" t="n"/>
+      <c r="M143" s="5" t="n"/>
+      <c r="N143" s="5" t="n"/>
+      <c r="O143" s="5" t="n"/>
+      <c r="P143" s="5" t="n"/>
       <c r="Q143" s="5" t="inlineStr">
         <is>
           <t>D0=182.97; 最新=2026-06-01; 相对D0=-3.43%; 本次触发=2026-05-28(正式卖出)</t>
@@ -9816,24 +7902,6 @@
       <c r="J144" t="n">
         <v>492.29</v>
       </c>
-      <c r="K144" t="n">
-        <v/>
-      </c>
-      <c r="L144" t="n">
-        <v/>
-      </c>
-      <c r="M144" t="n">
-        <v/>
-      </c>
-      <c r="N144" t="n">
-        <v/>
-      </c>
-      <c r="O144" t="n">
-        <v/>
-      </c>
-      <c r="P144" t="n">
-        <v/>
-      </c>
       <c r="Q144" t="inlineStr">
         <is>
           <t>D0=480.64; 最新=2026-06-01; 相对D0=2.42%; 本次触发=2026-05-28(正式卖出 | 预警卖出)</t>
@@ -9885,24 +7953,12 @@
       <c r="J145" s="5" t="n">
         <v>93.62</v>
       </c>
-      <c r="K145" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L145" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M145" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N145" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O145" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P145" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K145" s="5" t="n"/>
+      <c r="L145" s="5" t="n"/>
+      <c r="M145" s="5" t="n"/>
+      <c r="N145" s="5" t="n"/>
+      <c r="O145" s="5" t="n"/>
+      <c r="P145" s="5" t="n"/>
       <c r="Q145" s="5" t="inlineStr">
         <is>
           <t>D0=92.33; 最新=2026-06-01; 相对D0=1.40%; 本次触发=2026-05-29(正式卖出 | 预警卖出)</t>
@@ -9954,24 +8010,12 @@
       <c r="J146" s="5" t="n">
         <v>72.75</v>
       </c>
-      <c r="K146" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L146" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M146" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N146" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O146" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P146" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K146" s="5" t="n"/>
+      <c r="L146" s="5" t="n"/>
+      <c r="M146" s="5" t="n"/>
+      <c r="N146" s="5" t="n"/>
+      <c r="O146" s="5" t="n"/>
+      <c r="P146" s="5" t="n"/>
       <c r="Q146" s="5" t="inlineStr">
         <is>
           <t>D0=69.56; 最新=2026-06-01; 相对D0=4.59%; 本次触发=2026-05-29(正式卖出 | 预警卖出)</t>
@@ -10023,24 +8067,12 @@
       <c r="J147" s="5" t="n">
         <v>273.51</v>
       </c>
-      <c r="K147" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L147" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M147" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N147" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O147" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P147" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K147" s="5" t="n"/>
+      <c r="L147" s="5" t="n"/>
+      <c r="M147" s="5" t="n"/>
+      <c r="N147" s="5" t="n"/>
+      <c r="O147" s="5" t="n"/>
+      <c r="P147" s="5" t="n"/>
       <c r="Q147" s="5" t="inlineStr">
         <is>
           <t>D0=285.00; 最新=2026-06-01; 相对D0=-4.03%; 本次触发=2026-05-29(正式卖出)</t>
@@ -10092,24 +8124,12 @@
       <c r="J148" s="5" t="n">
         <v>362.9</v>
       </c>
-      <c r="K148" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L148" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M148" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N148" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O148" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P148" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K148" s="5" t="n"/>
+      <c r="L148" s="5" t="n"/>
+      <c r="M148" s="5" t="n"/>
+      <c r="N148" s="5" t="n"/>
+      <c r="O148" s="5" t="n"/>
+      <c r="P148" s="5" t="n"/>
       <c r="Q148" s="5" t="inlineStr">
         <is>
           <t>D0=361.47; 最新=2026-06-01; 相对D0=0.40%; 本次触发=2026-05-29(正式卖出)</t>
@@ -10161,24 +8181,12 @@
       <c r="J149" s="5" t="n">
         <v>27.15</v>
       </c>
-      <c r="K149" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L149" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M149" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N149" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O149" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P149" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K149" s="5" t="n"/>
+      <c r="L149" s="5" t="n"/>
+      <c r="M149" s="5" t="n"/>
+      <c r="N149" s="5" t="n"/>
+      <c r="O149" s="5" t="n"/>
+      <c r="P149" s="5" t="n"/>
       <c r="Q149" s="5" t="inlineStr">
         <is>
           <t>D0=18.88; 最新=2026-06-01; 相对D0=43.80%; 本次触发=2026-05-29(正式卖出 | 预警卖出)</t>
@@ -10230,24 +8238,6 @@
       <c r="J150" t="n">
         <v>109.33</v>
       </c>
-      <c r="K150" t="n">
-        <v/>
-      </c>
-      <c r="L150" t="n">
-        <v/>
-      </c>
-      <c r="M150" t="n">
-        <v/>
-      </c>
-      <c r="N150" t="n">
-        <v/>
-      </c>
-      <c r="O150" t="n">
-        <v/>
-      </c>
-      <c r="P150" t="n">
-        <v/>
-      </c>
       <c r="Q150" t="inlineStr">
         <is>
           <t>D0=114.68; 最新=2026-06-01; 相对D0=-4.67%; 本次触发=2026-05-29(正式卖出 | 预警卖出)</t>
@@ -10299,24 +8289,12 @@
       <c r="J151" s="5" t="n">
         <v>129.47</v>
       </c>
-      <c r="K151" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L151" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M151" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N151" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O151" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P151" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K151" s="5" t="n"/>
+      <c r="L151" s="5" t="n"/>
+      <c r="M151" s="5" t="n"/>
+      <c r="N151" s="5" t="n"/>
+      <c r="O151" s="5" t="n"/>
+      <c r="P151" s="5" t="n"/>
       <c r="Q151" s="5" t="inlineStr">
         <is>
           <t>D0=134.08; 最新=2026-06-01; 相对D0=-3.44%; 本次触发=2026-05-29(正式卖出 | 预警卖出)</t>
@@ -10368,24 +8346,12 @@
       <c r="J152" s="5" t="n">
         <v>252.53</v>
       </c>
-      <c r="K152" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L152" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M152" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N152" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O152" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P152" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K152" s="5" t="n"/>
+      <c r="L152" s="5" t="n"/>
+      <c r="M152" s="5" t="n"/>
+      <c r="N152" s="5" t="n"/>
+      <c r="O152" s="5" t="n"/>
+      <c r="P152" s="5" t="n"/>
       <c r="Q152" s="5" t="inlineStr">
         <is>
           <t>D0=255.23; 最新=2026-06-01; 相对D0=-1.06%; 本次触发=2026-05-29(正式卖出)</t>
@@ -10437,24 +8403,6 @@
       <c r="J153" t="n">
         <v>105.65</v>
       </c>
-      <c r="K153" t="n">
-        <v/>
-      </c>
-      <c r="L153" t="n">
-        <v/>
-      </c>
-      <c r="M153" t="n">
-        <v/>
-      </c>
-      <c r="N153" t="n">
-        <v/>
-      </c>
-      <c r="O153" t="n">
-        <v/>
-      </c>
-      <c r="P153" t="n">
-        <v/>
-      </c>
       <c r="Q153" t="inlineStr">
         <is>
           <t>D0=105.65; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式卖出)</t>
@@ -10506,24 +8454,12 @@
       <c r="J154" s="5" t="n">
         <v>163.09</v>
       </c>
-      <c r="K154" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L154" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M154" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N154" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O154" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P154" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K154" s="5" t="n"/>
+      <c r="L154" s="5" t="n"/>
+      <c r="M154" s="5" t="n"/>
+      <c r="N154" s="5" t="n"/>
+      <c r="O154" s="5" t="n"/>
+      <c r="P154" s="5" t="n"/>
       <c r="Q154" s="5" t="inlineStr">
         <is>
           <t>D0=163.09; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式卖出)</t>
@@ -10575,24 +8511,6 @@
       <c r="J155" t="n">
         <v>64.61</v>
       </c>
-      <c r="K155" t="n">
-        <v/>
-      </c>
-      <c r="L155" t="n">
-        <v/>
-      </c>
-      <c r="M155" t="n">
-        <v/>
-      </c>
-      <c r="N155" t="n">
-        <v/>
-      </c>
-      <c r="O155" t="n">
-        <v/>
-      </c>
-      <c r="P155" t="n">
-        <v/>
-      </c>
       <c r="Q155" t="inlineStr">
         <is>
           <t>D0=64.61; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式卖出)</t>
@@ -10644,24 +8562,12 @@
       <c r="J156" s="5" t="n">
         <v>135.73</v>
       </c>
-      <c r="K156" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L156" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M156" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N156" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O156" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P156" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K156" s="5" t="n"/>
+      <c r="L156" s="5" t="n"/>
+      <c r="M156" s="5" t="n"/>
+      <c r="N156" s="5" t="n"/>
+      <c r="O156" s="5" t="n"/>
+      <c r="P156" s="5" t="n"/>
       <c r="Q156" s="5" t="inlineStr">
         <is>
           <t>D0=135.73; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式卖出 | 预警卖出)</t>
@@ -10713,24 +8619,6 @@
       <c r="J157" t="n">
         <v>600.47</v>
       </c>
-      <c r="K157" t="n">
-        <v/>
-      </c>
-      <c r="L157" t="n">
-        <v/>
-      </c>
-      <c r="M157" t="n">
-        <v/>
-      </c>
-      <c r="N157" t="n">
-        <v/>
-      </c>
-      <c r="O157" t="n">
-        <v/>
-      </c>
-      <c r="P157" t="n">
-        <v/>
-      </c>
       <c r="Q157" t="inlineStr">
         <is>
           <t>D0=600.47; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式卖出 | 预警卖出)</t>
@@ -10782,24 +8670,12 @@
       <c r="J158" s="5" t="n">
         <v>24.86</v>
       </c>
-      <c r="K158" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L158" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M158" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N158" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O158" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P158" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K158" s="5" t="n"/>
+      <c r="L158" s="5" t="n"/>
+      <c r="M158" s="5" t="n"/>
+      <c r="N158" s="5" t="n"/>
+      <c r="O158" s="5" t="n"/>
+      <c r="P158" s="5" t="n"/>
       <c r="Q158" s="5" t="inlineStr">
         <is>
           <t>D0=24.86; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式卖出)</t>
@@ -10850,24 +8726,6 @@
       </c>
       <c r="J159" t="n">
         <v>415.88</v>
-      </c>
-      <c r="K159" t="n">
-        <v/>
-      </c>
-      <c r="L159" t="n">
-        <v/>
-      </c>
-      <c r="M159" t="n">
-        <v/>
-      </c>
-      <c r="N159" t="n">
-        <v/>
-      </c>
-      <c r="O159" t="n">
-        <v/>
-      </c>
-      <c r="P159" t="n">
-        <v/>
       </c>
       <c r="Q159" t="inlineStr">
         <is>
@@ -10965,7 +8823,6 @@
         <v>2</v>
       </c>
     </row>
-    <row r="168"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10977,7 +8834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L45"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -11513,7 +9370,6 @@
       <c r="K12" s="11" t="n">
         <v>0.069425</v>
       </c>
-      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -11542,7 +9398,6 @@
       <c r="F13" t="n">
         <v>290.01</v>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>285</v>
       </c>
@@ -11555,7 +9410,6 @@
       <c r="K13" s="20" t="n">
         <v>-0.056895</v>
       </c>
-      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -11584,7 +9438,6 @@
       <c r="F14" t="n">
         <v>67.38</v>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>66.94</v>
       </c>
@@ -11597,7 +9450,6 @@
       <c r="K14" s="20" t="n">
         <v>-0.04111</v>
       </c>
-      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -12059,9 +9911,7 @@
           <t>AXTI</t>
         </is>
       </c>
-      <c r="B33" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B33" s="21" t="n"/>
       <c r="C33" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -12101,9 +9951,7 @@
           <t>CEG</t>
         </is>
       </c>
-      <c r="B34" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B34" s="21" t="n"/>
       <c r="C34" s="5" t="inlineStr">
         <is>
           <t>08 核能</t>
@@ -12143,9 +9991,7 @@
           <t>GLW</t>
         </is>
       </c>
-      <c r="B35" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B35" s="21" t="n"/>
       <c r="C35" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -12185,9 +10031,7 @@
           <t>SNPS</t>
         </is>
       </c>
-      <c r="B36" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B36" s="21" t="n"/>
       <c r="C36" s="5" t="inlineStr">
         <is>
           <t>04 半导体设备 / EDA</t>
@@ -12285,9 +10129,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12299,7 +10140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -12506,7 +10347,7 @@
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F6" s="12" t="n">
@@ -12708,7 +10549,6 @@
       <c r="F11" t="n">
         <v>211.14</v>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>224.36</v>
       </c>
@@ -12864,14 +10704,12 @@
       <c r="F15" t="n">
         <v>1921.71</v>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>1940.04</v>
       </c>
       <c r="I15" s="11" t="n">
         <v>0.009538</v>
       </c>
-      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16"/>
     <row r="17">
@@ -13029,9 +10867,7 @@
           <t>AEHR</t>
         </is>
       </c>
-      <c r="B27" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B27" s="21" t="n"/>
       <c r="C27" s="5" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -13065,9 +10901,7 @@
           <t>AMKR</t>
         </is>
       </c>
-      <c r="B28" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B28" s="21" t="n"/>
       <c r="C28" s="5" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -13101,9 +10935,7 @@
           <t>BE</t>
         </is>
       </c>
-      <c r="B29" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B29" s="21" t="n"/>
       <c r="C29" s="5" t="inlineStr">
         <is>
           <t>09 储能</t>
@@ -13137,9 +10969,7 @@
           <t>COHR</t>
         </is>
       </c>
-      <c r="B30" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B30" s="21" t="n"/>
       <c r="C30" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -13173,9 +11003,7 @@
           <t>FLNC</t>
         </is>
       </c>
-      <c r="B31" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B31" s="21" t="n"/>
       <c r="C31" s="5" t="inlineStr">
         <is>
           <t>09 储能</t>
@@ -13209,9 +11037,7 @@
           <t>INTC</t>
         </is>
       </c>
-      <c r="B32" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B32" s="21" t="n"/>
       <c r="C32" s="5" t="inlineStr">
         <is>
           <t>03 GPU / AI芯片</t>
@@ -13245,9 +11071,7 @@
           <t>NRG</t>
         </is>
       </c>
-      <c r="B33" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B33" s="21" t="n"/>
       <c r="C33" s="5" t="inlineStr">
         <is>
           <t>07 数据中心电力</t>
@@ -13281,9 +11105,7 @@
           <t>TSEM</t>
         </is>
       </c>
-      <c r="B34" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B34" s="21" t="n"/>
       <c r="C34" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -13401,7 +11223,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13413,7 +11234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -13496,7 +11317,7 @@
       </c>
       <c r="E3" s="14" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F3" s="12" t="n">
@@ -13626,8 +11447,6 @@
       <c r="F7" t="n">
         <v>69.56999999999999</v>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
@@ -13750,8 +11569,6 @@
       <c r="F11" t="n">
         <v>15.58</v>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -13810,8 +11627,6 @@
       <c r="F13" t="n">
         <v>323.39</v>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -14104,8 +11919,6 @@
       <c r="F22" t="n">
         <v>14.7</v>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
@@ -14283,9 +12096,7 @@
           <t>ASTS</t>
         </is>
       </c>
-      <c r="B35" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B35" s="21" t="n"/>
       <c r="C35" s="5" t="inlineStr">
         <is>
           <t>17 高弹性交易池</t>
@@ -14313,9 +12124,7 @@
           <t>CAMT</t>
         </is>
       </c>
-      <c r="B36" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B36" s="21" t="n"/>
       <c r="C36" s="5" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -14343,9 +12152,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B37" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B37" s="21" t="n"/>
       <c r="C37" s="5" t="inlineStr">
         <is>
           <t>15 公用事业</t>
@@ -14373,9 +12180,7 @@
           <t>ENTG</t>
         </is>
       </c>
-      <c r="B38" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B38" s="21" t="n"/>
       <c r="C38" s="5" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -14403,9 +12208,7 @@
           <t>META</t>
         </is>
       </c>
-      <c r="B39" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B39" s="21" t="n"/>
       <c r="C39" s="5" t="inlineStr">
         <is>
           <t>02 超巨</t>
@@ -14433,9 +12236,7 @@
           <t>NVTS</t>
         </is>
       </c>
-      <c r="B40" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B40" s="21" t="n"/>
       <c r="C40" s="5" t="inlineStr">
         <is>
           <t>07 数据中心电力</t>
@@ -14463,9 +12264,7 @@
           <t>TSLA</t>
         </is>
       </c>
-      <c r="B41" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B41" s="21" t="n"/>
       <c r="C41" s="5" t="inlineStr">
         <is>
           <t>02 超巨</t>
@@ -14577,7 +12376,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14885,7 +12683,6 @@
       <c r="V3" t="n">
         <v>85.45999908447266</v>
       </c>
-      <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=51.78; 4H分金=49.43</t>
@@ -14967,8 +12764,6 @@
       <c r="T4" t="b">
         <v>0</v>
       </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
         <v>91</v>
       </c>
@@ -15053,8 +12848,6 @@
       <c r="T5" t="b">
         <v>0</v>
       </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
         <v>90</v>
       </c>
@@ -15093,7 +12886,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -15319,8 +13112,6 @@
       <c r="T8" t="b">
         <v>0</v>
       </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
         <v>90</v>
       </c>
@@ -15585,9 +13376,6 @@
       <c r="T11" t="b">
         <v>1</v>
       </c>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=45.16; 4H分金=48.27</t>
@@ -15669,8 +13457,6 @@
       <c r="T12" t="b">
         <v>0</v>
       </c>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
       <c r="W12" t="n">
         <v>86</v>
       </c>
@@ -15935,8 +13721,6 @@
       <c r="T15" t="b">
         <v>0</v>
       </c>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
       <c r="W15" t="n">
         <v>90</v>
       </c>
@@ -16021,9 +13805,6 @@
       <c r="T16" t="b">
         <v>1</v>
       </c>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=48.07; 4H分金=49.33</t>
@@ -16111,7 +13892,6 @@
       <c r="V17" t="n">
         <v>43.59000015258789</v>
       </c>
-      <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-20; 1出价格=43.59; Gann0=38.83; 段涨幅=12.26%</t>
@@ -16373,8 +14153,6 @@
       <c r="T20" t="b">
         <v>0</v>
       </c>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
       <c r="W20" t="n">
         <v>98</v>
       </c>
@@ -16549,8 +14327,6 @@
       <c r="T22" t="b">
         <v>0</v>
       </c>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
       <c r="W22" t="n">
         <v>89</v>
       </c>
@@ -16679,7 +14455,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -16769,7 +14545,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -17175,8 +14951,6 @@
       <c r="T29" t="b">
         <v>0</v>
       </c>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
       <c r="W29" t="n">
         <v>88</v>
       </c>
@@ -17351,8 +15125,6 @@
       <c r="T31" t="b">
         <v>0</v>
       </c>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
       <c r="W31" t="n">
         <v>91</v>
       </c>
@@ -17443,7 +15215,6 @@
       <c r="V32" t="n">
         <v>15.39999961853027</v>
       </c>
-      <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=54.98; 4H分金=49.65</t>
@@ -17531,7 +15302,6 @@
       <c r="V33" t="n">
         <v>105.5599975585938</v>
       </c>
-      <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=50.29; 4H分金=48.73</t>
@@ -17613,8 +15383,6 @@
       <c r="T34" t="b">
         <v>0</v>
       </c>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
       <c r="W34" t="n">
         <v>86</v>
       </c>
@@ -17969,8 +15737,6 @@
       <c r="T38" t="b">
         <v>0</v>
       </c>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
       <c r="W38" t="n">
         <v>98</v>
       </c>
@@ -18189,7 +15955,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -18325,8 +16091,6 @@
       <c r="T42" t="b">
         <v>0</v>
       </c>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
       <c r="W42" t="n">
         <v>88</v>
       </c>
@@ -18417,7 +16181,6 @@
       <c r="V43" t="n">
         <v>194.9600067138672</v>
       </c>
-      <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=50.57; 4H分金=48.78</t>
@@ -18685,7 +16448,6 @@
       <c r="V46" t="n">
         <v>269.7900085449219</v>
       </c>
-      <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=50.14; 4H分金=49.53</t>
@@ -18773,7 +16535,6 @@
       <c r="V47" t="n">
         <v>330.2200012207031</v>
       </c>
-      <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=49.16; 4H分金=41.08</t>
@@ -19125,8 +16886,6 @@
       <c r="T51" t="b">
         <v>0</v>
       </c>
-      <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
       <c r="W51" t="n">
         <v>89</v>
       </c>
@@ -19301,8 +17060,6 @@
       <c r="T53" t="b">
         <v>0</v>
       </c>
-      <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
       <c r="W53" t="n">
         <v>90</v>
       </c>
@@ -19387,8 +17144,6 @@
       <c r="T54" t="b">
         <v>0</v>
       </c>
-      <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
       <c r="W54" t="n">
         <v>94</v>
       </c>
@@ -19479,7 +17234,6 @@
       <c r="V55" t="n">
         <v>198.8699951171875</v>
       </c>
-      <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-19; 1出价格=198.87; Gann0=179.53; 段涨幅=10.77%</t>
@@ -19657,7 +17411,6 @@
       <c r="V57" t="n">
         <v>145.6999969482422</v>
       </c>
-      <c r="W57" t="inlineStr"/>
       <c r="X57" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-20; 1出价格=145.70; Gann0=128.83; 段涨幅=13.09%</t>
@@ -20195,7 +17948,6 @@
       <c r="V63" t="n">
         <v>977.27001953125</v>
       </c>
-      <c r="W63" t="inlineStr"/>
       <c r="X63" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=47.01; 4H分金=41.40</t>
@@ -20277,9 +18029,6 @@
       <c r="T64" t="b">
         <v>1</v>
       </c>
-      <c r="U64" t="inlineStr"/>
-      <c r="V64" t="inlineStr"/>
-      <c r="W64" t="inlineStr"/>
       <c r="X64" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=40.99; 4H分金=34.86</t>
@@ -20457,7 +18206,6 @@
       <c r="V66" t="n">
         <v>349.2099914550781</v>
       </c>
-      <c r="W66" t="inlineStr"/>
       <c r="X66" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-19; 1出价格=349.21; Gann0=244.88; 段涨幅=42.60%</t>
@@ -20583,7 +18331,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -20725,7 +18473,6 @@
       <c r="V69" t="n">
         <v>226.8099975585938</v>
       </c>
-      <c r="W69" t="inlineStr"/>
       <c r="X69" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=55.20; 4H分金=48.61</t>
@@ -20903,7 +18650,6 @@
       <c r="V71" t="n">
         <v>110.8300018310547</v>
       </c>
-      <c r="W71" t="inlineStr"/>
       <c r="X71" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=56.16; 4H分金=48.24</t>
@@ -20939,7 +18685,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -21261,7 +19007,6 @@
       <c r="V75" t="n">
         <v>61.2400016784668</v>
       </c>
-      <c r="W75" t="inlineStr"/>
       <c r="X75" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-20; 1出价格=61.24; Gann0=52.99; 段涨幅=15.57%</t>
@@ -21439,7 +19184,6 @@
       <c r="V77" t="n">
         <v>15.39999961853027</v>
       </c>
-      <c r="W77" t="inlineStr"/>
       <c r="X77" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-22; 1出价格=15.40; Gann0=11.82; 段涨幅=30.29%</t>
@@ -21655,7 +19399,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -21835,7 +19579,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -22247,7 +19991,6 @@
       <c r="V86" t="n">
         <v>88.55000305175781</v>
       </c>
-      <c r="W86" t="inlineStr"/>
       <c r="X86" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=50.93; 4H分金=48.13</t>
@@ -22329,8 +20072,6 @@
       <c r="T87" t="b">
         <v>0</v>
       </c>
-      <c r="U87" t="inlineStr"/>
-      <c r="V87" t="inlineStr"/>
       <c r="W87" t="n">
         <v>100</v>
       </c>
@@ -22511,7 +20252,6 @@
       <c r="V89" t="n">
         <v>61.70000076293945</v>
       </c>
-      <c r="W89" t="inlineStr"/>
       <c r="X89" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-20; 1出价格=61.70; Gann0=55.13; 段涨幅=11.92%</t>
@@ -22959,7 +20699,6 @@
       <c r="V94" t="n">
         <v>143.1600036621094</v>
       </c>
-      <c r="W94" t="inlineStr"/>
       <c r="X94" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=54.24; 4H分金=47.86</t>
@@ -23047,7 +20786,6 @@
       <c r="V95" t="n">
         <v>322.8299865722656</v>
       </c>
-      <c r="W95" t="inlineStr"/>
       <c r="X95" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=53.51; 4H分金=46.81</t>
@@ -23135,7 +20873,6 @@
       <c r="V96" t="n">
         <v>310.4500122070312</v>
       </c>
-      <c r="W96" t="inlineStr"/>
       <c r="X96" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=50.07; 4H分金=49.25</t>
@@ -23223,7 +20960,6 @@
       <c r="V97" t="n">
         <v>84.98999786376953</v>
       </c>
-      <c r="W97" t="inlineStr"/>
       <c r="X97" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=65.41; 4H分金=46.13</t>
@@ -23491,7 +21227,6 @@
       <c r="V100" t="n">
         <v>183.9199981689453</v>
       </c>
-      <c r="W100" t="inlineStr"/>
       <c r="X100" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=49.34; 4H分金=45.78</t>
@@ -23579,7 +21314,6 @@
       <c r="V101" t="n">
         <v>677.5</v>
       </c>
-      <c r="W101" t="inlineStr"/>
       <c r="X101" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=69.20; 4H分金=49.77</t>
@@ -23667,7 +21401,6 @@
       <c r="V102" t="n">
         <v>68.97000122070312</v>
       </c>
-      <c r="W102" t="inlineStr"/>
       <c r="X102" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=61.29; 4H分金=51.57</t>
@@ -23755,7 +21488,6 @@
       <c r="V103" t="n">
         <v>50.5</v>
       </c>
-      <c r="W103" t="inlineStr"/>
       <c r="X103" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=45.87; 4H分金=41.41</t>
@@ -23843,7 +21575,6 @@
       <c r="V104" t="n">
         <v>134.9100036621094</v>
       </c>
-      <c r="W104" t="inlineStr"/>
       <c r="X104" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=65.12; 4H分金=42.03</t>
@@ -23931,7 +21662,6 @@
       <c r="V105" t="n">
         <v>199.9299926757812</v>
       </c>
-      <c r="W105" t="inlineStr"/>
       <c r="X105" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=53.09; 4H分金=49.59</t>
@@ -24057,7 +21787,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -24379,7 +22109,6 @@
       <c r="V110" t="n">
         <v>94.91999816894531</v>
       </c>
-      <c r="W110" t="inlineStr"/>
       <c r="X110" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=58.51; 4H分金=49.40</t>
@@ -24641,9 +22370,6 @@
       <c r="T113" t="b">
         <v>1</v>
       </c>
-      <c r="U113" t="inlineStr"/>
-      <c r="V113" t="inlineStr"/>
-      <c r="W113" t="inlineStr"/>
       <c r="X113" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=44.82; 4H分金=47.70</t>
@@ -24731,7 +22457,6 @@
       <c r="V114" t="n">
         <v>521.22998046875</v>
       </c>
-      <c r="W114" t="inlineStr"/>
       <c r="X114" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=47.81; 4H分金=33.44</t>
@@ -24909,7 +22634,6 @@
       <c r="V116" t="n">
         <v>96.38999938964844</v>
       </c>
-      <c r="W116" t="inlineStr"/>
       <c r="X116" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=59.32; 4H分金=47.38</t>
@@ -25177,7 +22901,6 @@
       <c r="V119" t="n">
         <v>197</v>
       </c>
-      <c r="W119" t="inlineStr"/>
       <c r="X119" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=53.96; 4H分金=52.74</t>
@@ -25265,7 +22988,6 @@
       <c r="V120" t="n">
         <v>261.4100036621094</v>
       </c>
-      <c r="W120" t="inlineStr"/>
       <c r="X120" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=64.28; 4H分金=46.06</t>
@@ -25353,7 +23075,6 @@
       <c r="V121" t="n">
         <v>139.0200042724609</v>
       </c>
-      <c r="W121" t="inlineStr"/>
       <c r="X121" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=39.09; 4H分金=22.70</t>
@@ -25441,7 +23162,6 @@
       <c r="V122" t="n">
         <v>58.81999969482422</v>
       </c>
-      <c r="W122" t="inlineStr"/>
       <c r="X122" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-26; 1出价格=58.82; Gann0=52.73; 段涨幅=11.55%</t>
@@ -25529,7 +23249,6 @@
       <c r="V123" t="n">
         <v>58.81999969482422</v>
       </c>
-      <c r="W123" t="inlineStr"/>
       <c r="X123" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=50.71; 4H分金=39.07</t>
@@ -25655,7 +23374,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -25881,8 +23600,6 @@
       <c r="T127" t="b">
         <v>0</v>
       </c>
-      <c r="U127" t="inlineStr"/>
-      <c r="V127" t="inlineStr"/>
       <c r="W127" t="n">
         <v>81</v>
       </c>
@@ -25973,7 +23690,6 @@
       <c r="V128" t="n">
         <v>191.25</v>
       </c>
-      <c r="W128" t="inlineStr"/>
       <c r="X128" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-26; 1出价格=191.25; Gann0=127.79; 段涨幅=49.66%</t>
@@ -26061,7 +23777,6 @@
       <c r="V129" t="n">
         <v>191.25</v>
       </c>
-      <c r="W129" t="inlineStr"/>
       <c r="X129" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=31.56; 4H分金=18.97</t>
@@ -26149,7 +23864,6 @@
       <c r="V130" t="n">
         <v>143.1600036621094</v>
       </c>
-      <c r="W130" t="inlineStr"/>
       <c r="X130" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-26; 1出价格=143.16; Gann0=101.88; 段涨幅=40.52%</t>
@@ -26417,7 +24131,6 @@
       <c r="V133" t="n">
         <v>310.4500122070312</v>
       </c>
-      <c r="W133" t="inlineStr"/>
       <c r="X133" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-26; 1出价格=310.45; Gann0=256.10; 段涨幅=21.22%</t>
@@ -26595,7 +24308,6 @@
       <c r="V135" t="n">
         <v>393.5199890136719</v>
       </c>
-      <c r="W135" t="inlineStr"/>
       <c r="X135" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=54.60; 4H分金=49.67</t>
@@ -26677,8 +24389,6 @@
       <c r="T136" t="b">
         <v>0</v>
       </c>
-      <c r="U136" t="inlineStr"/>
-      <c r="V136" t="inlineStr"/>
       <c r="W136" t="n">
         <v>96</v>
       </c>
@@ -26853,8 +24563,6 @@
       <c r="T138" t="b">
         <v>0</v>
       </c>
-      <c r="U138" t="inlineStr"/>
-      <c r="V138" t="inlineStr"/>
       <c r="W138" t="n">
         <v>85</v>
       </c>
@@ -27035,7 +24743,6 @@
       <c r="V140" t="n">
         <v>125.9499969482422</v>
       </c>
-      <c r="W140" t="inlineStr"/>
       <c r="X140" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=43.41; 4H分金=33.44</t>
@@ -27213,7 +24920,6 @@
       <c r="V142" t="n">
         <v>199.9299926757812</v>
       </c>
-      <c r="W142" t="inlineStr"/>
       <c r="X142" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-26; 1出价格=199.93; Gann0=169.80; 段涨幅=17.74%</t>
@@ -28741,7 +26447,6 @@
       <c r="V159" t="n">
         <v>539.47998046875</v>
       </c>
-      <c r="W159" t="inlineStr"/>
       <c r="X159" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-26; 1出价格=539.48; Gann0=473.77; 段涨幅=13.87%</t>
@@ -28829,7 +26534,6 @@
       <c r="V160" t="n">
         <v>539.47998046875</v>
       </c>
-      <c r="W160" t="inlineStr"/>
       <c r="X160" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=38.34; 4H分金=25.68</t>
@@ -28917,7 +26621,6 @@
       <c r="V161" t="n">
         <v>302.8599853515625</v>
       </c>
-      <c r="W161" t="inlineStr"/>
       <c r="X161" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=59.03; 4H分金=49.91</t>
@@ -29005,7 +26708,6 @@
       <c r="V162" t="n">
         <v>45.63999938964844</v>
       </c>
-      <c r="W162" t="inlineStr"/>
       <c r="X162" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=42.99; 4H分金=32.45</t>
@@ -29131,7 +26833,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -29363,7 +27065,6 @@
       <c r="V166" t="n">
         <v>112</v>
       </c>
-      <c r="W166" t="inlineStr"/>
       <c r="X166" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-27; 1出价格=112.00; Gann0=76.76; 段涨幅=45.91%</t>
@@ -29451,7 +27152,6 @@
       <c r="V167" t="n">
         <v>112</v>
       </c>
-      <c r="W167" t="inlineStr"/>
       <c r="X167" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=46.51; 4H分金=34.98</t>
@@ -29539,7 +27239,6 @@
       <c r="V168" t="n">
         <v>14.73999977111816</v>
       </c>
-      <c r="W168" t="inlineStr"/>
       <c r="X168" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=63.89; 4H分金=51.21</t>
@@ -29627,7 +27326,6 @@
       <c r="V169" t="n">
         <v>76.30000305175781</v>
       </c>
-      <c r="W169" t="inlineStr"/>
       <c r="X169" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-26; 1出价格=76.30; Gann0=62.45; 段涨幅=22.18%</t>
@@ -29715,7 +27413,6 @@
       <c r="V170" t="n">
         <v>76.30000305175781</v>
       </c>
-      <c r="W170" t="inlineStr"/>
       <c r="X170" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=48.17; 4H分金=45.51</t>
@@ -29803,7 +27500,6 @@
       <c r="V171" t="n">
         <v>133.8600006103516</v>
       </c>
-      <c r="W171" t="inlineStr"/>
       <c r="X171" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=58.46; 4H分金=46.97</t>
@@ -29891,7 +27587,6 @@
       <c r="V172" t="n">
         <v>322.8299865722656</v>
       </c>
-      <c r="W172" t="inlineStr"/>
       <c r="X172" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-22; 1出价格=322.83; Gann0=241.75; 段涨幅=33.54%</t>
@@ -30069,7 +27764,6 @@
       <c r="V174" t="n">
         <v>178.9100036621094</v>
       </c>
-      <c r="W174" t="inlineStr"/>
       <c r="X174" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=50.41; 4H分金=56.01</t>
@@ -30247,7 +27941,6 @@
       <c r="V176" t="n">
         <v>393.5199890136719</v>
       </c>
-      <c r="W176" t="inlineStr"/>
       <c r="X176" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-28; 1出价格=393.52; Gann0=336.70; 段涨幅=16.88%</t>
@@ -30965,7 +28658,6 @@
       <c r="V184" t="n">
         <v>9.319999694824219</v>
       </c>
-      <c r="W184" t="inlineStr"/>
       <c r="X184" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=55.35; 4H分金=48.97</t>
@@ -31053,7 +28745,6 @@
       <c r="V185" t="n">
         <v>22.48999977111816</v>
       </c>
-      <c r="W185" t="inlineStr"/>
       <c r="X185" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-22; 1出价格=22.49; Gann0=17.23; 段涨幅=30.51%</t>
@@ -31141,7 +28832,6 @@
       <c r="V186" t="n">
         <v>22.48999977111816</v>
       </c>
-      <c r="W186" t="inlineStr"/>
       <c r="X186" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=44.73; 4H分金=28.42</t>
@@ -31229,7 +28919,6 @@
       <c r="V187" t="n">
         <v>391.8699951171875</v>
       </c>
-      <c r="W187" t="inlineStr"/>
       <c r="X187" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=41.55; 4H分金=26.60</t>
@@ -31317,7 +29006,6 @@
       <c r="V188" t="n">
         <v>126.6399993896484</v>
       </c>
-      <c r="W188" t="inlineStr"/>
       <c r="X188" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-29; 1出价格=126.64; Gann0=102.40; 段涨幅=23.67%</t>
@@ -31405,7 +29093,6 @@
       <c r="V189" t="n">
         <v>126.6399993896484</v>
       </c>
-      <c r="W189" t="inlineStr"/>
       <c r="X189" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=48.85; 4H分金=32.32</t>
@@ -31583,7 +29270,6 @@
       <c r="V191" t="n">
         <v>2060.080078125</v>
       </c>
-      <c r="W191" t="inlineStr"/>
       <c r="X191" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=56.18; 4H分金=51.85</t>
@@ -31671,7 +29357,6 @@
       <c r="V192" t="n">
         <v>188.1999969482422</v>
       </c>
-      <c r="W192" t="inlineStr"/>
       <c r="X192" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=46.91; 4H分金=49.93</t>
@@ -31849,7 +29534,6 @@
       <c r="V194" t="n">
         <v>143.0800018310547</v>
       </c>
-      <c r="W194" t="inlineStr"/>
       <c r="X194" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-26; 1出价格=143.08; Gann0=121.22; 段涨幅=18.03%</t>
@@ -31937,7 +29621,6 @@
       <c r="V195" t="n">
         <v>143.0800018310547</v>
       </c>
-      <c r="W195" t="inlineStr"/>
       <c r="X195" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=43.56; 4H分金=35.42</t>
@@ -32019,8 +29702,6 @@
       <c r="T196" t="b">
         <v>0</v>
       </c>
-      <c r="U196" t="inlineStr"/>
-      <c r="V196" t="inlineStr"/>
       <c r="W196" t="n">
         <v>88</v>
       </c>
@@ -32111,7 +29792,6 @@
       <c r="V197" t="n">
         <v>33.81999969482422</v>
       </c>
-      <c r="W197" t="inlineStr"/>
       <c r="X197" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=56.55; 4H分金=43.70</t>
@@ -32199,7 +29879,6 @@
       <c r="V198" t="n">
         <v>73.29000091552734</v>
       </c>
-      <c r="W198" t="inlineStr"/>
       <c r="X198" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=50.01; 4H分金=47.34</t>
@@ -32377,7 +30056,6 @@
       <c r="V200" t="n">
         <v>406.6499938964844</v>
       </c>
-      <c r="W200" t="inlineStr"/>
       <c r="X200" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=55.90; 4H分金=55.39</t>
@@ -32465,7 +30143,6 @@
       <c r="V201" t="n">
         <v>302.8599853515625</v>
       </c>
-      <c r="W201" t="inlineStr"/>
       <c r="X201" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-26; 1出价格=302.86; Gann0=200.89; 段涨幅=50.76%</t>
@@ -32637,9 +30314,6 @@
       <c r="T203" t="b">
         <v>1</v>
       </c>
-      <c r="U203" t="inlineStr"/>
-      <c r="V203" t="inlineStr"/>
-      <c r="W203" t="inlineStr"/>
       <c r="X203" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=45.00; 4H分金=48.44</t>
@@ -33087,7 +30761,6 @@
       <c r="V208" t="n">
         <v>315</v>
       </c>
-      <c r="W208" t="inlineStr"/>
       <c r="X208" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=56.44; 4H分金=38.99</t>
@@ -33445,7 +31118,6 @@
       <c r="V212" t="n">
         <v>274.75</v>
       </c>
-      <c r="W212" t="inlineStr"/>
       <c r="X212" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=41.87; 4H分金=29.59</t>
@@ -33713,7 +31385,6 @@
       <c r="V215" t="n">
         <v>133.8600006103516</v>
       </c>
-      <c r="W215" t="inlineStr"/>
       <c r="X215" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-28; 1出价格=133.86; Gann0=69.92; 段涨幅=91.45%</t>
@@ -33801,7 +31472,6 @@
       <c r="V216" t="n">
         <v>178.9100036621094</v>
       </c>
-      <c r="W216" t="inlineStr"/>
       <c r="X216" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-27; 1出价格=178.91; Gann0=147.57; 段涨幅=21.24%</t>
@@ -33883,8 +31553,6 @@
       <c r="T217" t="b">
         <v>0</v>
       </c>
-      <c r="U217" t="inlineStr"/>
-      <c r="V217" t="inlineStr"/>
       <c r="W217" t="n">
         <v>94</v>
       </c>
@@ -33975,7 +31643,6 @@
       <c r="V218" t="n">
         <v>68.97000122070312</v>
       </c>
-      <c r="W218" t="inlineStr"/>
       <c r="X218" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-18; 1出价格=68.97; Gann0=61.71; 段涨幅=11.76%</t>
@@ -34063,7 +31730,6 @@
       <c r="V219" t="n">
         <v>73.73999786376953</v>
       </c>
-      <c r="W219" t="inlineStr"/>
       <c r="X219" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=61.65; 4H分金=39.11</t>
@@ -34151,7 +31817,6 @@
       <c r="V220" t="n">
         <v>149.3099975585938</v>
       </c>
-      <c r="W220" t="inlineStr"/>
       <c r="X220" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-27; 1出价格=149.31; Gann0=122.00; 段涨幅=22.39%</t>
@@ -34239,7 +31904,6 @@
       <c r="V221" t="n">
         <v>149.3099975585938</v>
       </c>
-      <c r="W221" t="inlineStr"/>
       <c r="X221" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=46.17; 4H分金=37.91</t>
@@ -34321,8 +31985,6 @@
       <c r="T222" t="b">
         <v>0</v>
       </c>
-      <c r="U222" t="inlineStr"/>
-      <c r="V222" t="inlineStr"/>
       <c r="W222" t="n">
         <v>86</v>
       </c>
@@ -34503,7 +32165,6 @@
       <c r="V224" t="n">
         <v>409.6499938964844</v>
       </c>
-      <c r="W224" t="inlineStr"/>
       <c r="X224" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=50.92; 4H分金=50.49</t>
@@ -34989,7 +32650,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -35395,8 +33056,6 @@
       <c r="T234" t="b">
         <v>0</v>
       </c>
-      <c r="U234" t="inlineStr"/>
-      <c r="V234" t="inlineStr"/>
       <c r="W234" t="n">
         <v>91</v>
       </c>
@@ -35487,7 +33146,6 @@
       <c r="V235" t="n">
         <v>11.90999984741211</v>
       </c>
-      <c r="W235" t="inlineStr"/>
       <c r="X235" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=59.02; 4H分金=49.87</t>
@@ -35575,7 +33233,6 @@
       <c r="V236" t="n">
         <v>643</v>
       </c>
-      <c r="W236" t="inlineStr"/>
       <c r="X236" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-28; 1出价格=643.00; Gann0=594.81; 段涨幅=8.10%</t>
@@ -35663,7 +33320,6 @@
       <c r="V237" t="n">
         <v>643</v>
       </c>
-      <c r="W237" t="inlineStr"/>
       <c r="X237" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=40.60; 4H分金=32.16</t>
@@ -35751,7 +33407,6 @@
       <c r="V238" t="n">
         <v>24.5</v>
       </c>
-      <c r="W238" t="inlineStr"/>
       <c r="X238" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=55.29; 4H分金=49.04</t>
@@ -35839,7 +33494,6 @@
       <c r="V239" t="n">
         <v>134.1100006103516</v>
       </c>
-      <c r="W239" t="inlineStr"/>
       <c r="X239" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=45.14; 4H分金=41.50</t>
@@ -35921,8 +33575,6 @@
       <c r="T240" t="b">
         <v>0</v>
       </c>
-      <c r="U240" t="inlineStr"/>
-      <c r="V240" t="inlineStr"/>
       <c r="W240" t="n">
         <v>95</v>
       </c>
@@ -36193,7 +33845,6 @@
       <c r="V243" t="n">
         <v>33.81999969482422</v>
       </c>
-      <c r="W243" t="inlineStr"/>
       <c r="X243" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-26; 1出价格=33.82; Gann0=17.50; 段涨幅=93.26%</t>
@@ -36551,7 +34202,6 @@
       <c r="V247" t="n">
         <v>56.84000015258789</v>
       </c>
-      <c r="W247" t="inlineStr"/>
       <c r="X247" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=50.79; 4H分金=45.24</t>
@@ -36909,7 +34559,6 @@
       <c r="V251" t="n">
         <v>16.76000022888184</v>
       </c>
-      <c r="W251" t="inlineStr"/>
       <c r="X251" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=58.29; 4H分金=52.30</t>
@@ -36997,7 +34646,6 @@
       <c r="V252" t="n">
         <v>86.43000030517578</v>
       </c>
-      <c r="W252" t="inlineStr"/>
       <c r="X252" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=50.54; 4H分金=45.20</t>
@@ -37085,7 +34733,6 @@
       <c r="V253" t="n">
         <v>394.6300048828125</v>
       </c>
-      <c r="W253" t="inlineStr"/>
       <c r="X253" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=54.55; 4H分金=50.76</t>
@@ -37173,7 +34820,6 @@
       <c r="V254" t="n">
         <v>445.6000061035156</v>
       </c>
-      <c r="W254" t="inlineStr"/>
       <c r="X254" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-27; 1出价格=445.60; Gann0=393.63; 段涨幅=13.20%</t>
@@ -37261,7 +34907,6 @@
       <c r="V255" t="n">
         <v>445.6000061035156</v>
       </c>
-      <c r="W255" t="inlineStr"/>
       <c r="X255" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=43.10; 4H分金=24.03</t>
@@ -37349,7 +34994,6 @@
       <c r="V256" t="n">
         <v>13.93000030517578</v>
       </c>
-      <c r="W256" t="inlineStr"/>
       <c r="X256" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=47.48; 4H分金=47.96</t>
@@ -37431,8 +35075,6 @@
       <c r="T257" t="b">
         <v>0</v>
       </c>
-      <c r="U257" t="inlineStr"/>
-      <c r="V257" t="inlineStr"/>
       <c r="W257" t="n">
         <v>86</v>
       </c>
@@ -37517,8 +35159,6 @@
       <c r="T258" t="b">
         <v>0</v>
       </c>
-      <c r="U258" t="inlineStr"/>
-      <c r="V258" t="inlineStr"/>
       <c r="W258" t="n">
         <v>91</v>
       </c>
@@ -37609,7 +35249,6 @@
       <c r="V259" t="n">
         <v>167.3999938964844</v>
       </c>
-      <c r="W259" t="inlineStr"/>
       <c r="X259" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=51.12; 4H分金=40.44</t>
@@ -37697,7 +35336,6 @@
       <c r="V260" t="n">
         <v>51.58000183105469</v>
       </c>
-      <c r="W260" t="inlineStr"/>
       <c r="X260" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=49.41; 4H分金=45.41</t>
@@ -38090,7 +35728,6 @@
       <c r="D3" s="8" t="n">
         <v>46170</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" s="8" t="n">
         <v>46170</v>
       </c>
@@ -38139,7 +35776,6 @@
           <t>19 COWOS</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" s="8" t="n">
         <v>46164</v>
       </c>
@@ -38248,7 +35884,6 @@
       <c r="D6" s="8" t="n">
         <v>46164</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" s="8" t="n">
         <v>46164</v>
       </c>
@@ -38354,7 +35989,6 @@
       <c r="D8" s="8" t="n">
         <v>46170</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" s="8" t="n">
         <v>46170</v>
       </c>
@@ -38406,7 +36040,6 @@
       <c r="D9" s="8" t="n">
         <v>46164</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" s="8" t="n">
         <v>46164</v>
       </c>
@@ -38458,7 +36091,6 @@
       <c r="D10" s="8" t="n">
         <v>46164</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" s="8" t="n">
         <v>46164</v>
       </c>
@@ -38949,7 +36581,6 @@
       <c r="I7" t="n">
         <v>2</v>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" s="8" t="n">
         <v>46171</v>
       </c>
@@ -39038,7 +36669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R53"/>
+  <dimension ref="A1:R48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -39187,7 +36818,6 @@
       <c r="F3" t="n">
         <v>22.51</v>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>22.62</v>
       </c>
@@ -39759,7 +37389,6 @@
       <c r="F12" t="n">
         <v>16.12</v>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>15.47</v>
       </c>
@@ -39887,7 +37516,6 @@
       <c r="F14" t="n">
         <v>610.26</v>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>612.34</v>
       </c>
@@ -39951,7 +37579,6 @@
       <c r="F15" t="n">
         <v>181.49</v>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>177.62</v>
       </c>
@@ -40327,7 +37954,6 @@
       <c r="F21" t="n">
         <v>58.81</v>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>57.46</v>
       </c>
@@ -40391,7 +38017,6 @@
       <c r="F22" t="n">
         <v>81.76000000000001</v>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>84.64</v>
       </c>
@@ -40449,7 +38074,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
@@ -40515,7 +38140,6 @@
       <c r="F24" t="n">
         <v>426.01</v>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>433.59</v>
       </c>
@@ -40546,7 +38170,6 @@
       <c r="Q24" s="20" t="n">
         <v>-0.023779</v>
       </c>
-      <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -40569,7 +38192,7 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
@@ -40639,7 +38262,6 @@
       <c r="F26" t="n">
         <v>141.22</v>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>136.2</v>
       </c>
@@ -40889,7 +38511,7 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
@@ -40949,7 +38571,7 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
@@ -41244,9 +38866,7 @@
           <t>HAL</t>
         </is>
       </c>
-      <c r="B44" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B44" s="21" t="n"/>
       <c r="C44" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -41336,11 +38956,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -41352,7 +38967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P52"/>
+  <dimension ref="A1:P49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -41599,7 +39214,7 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F5" s="12" t="n">
@@ -41717,7 +39332,6 @@
       <c r="F7" t="n">
         <v>105.89</v>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>104.27</v>
       </c>
@@ -42623,7 +40237,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -42658,7 +40272,6 @@
       <c r="O23" s="11" t="n">
         <v>0.031388</v>
       </c>
-      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -42681,7 +40294,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
@@ -42789,7 +40402,7 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
@@ -43012,9 +40625,7 @@
           <t>CVX</t>
         </is>
       </c>
-      <c r="B38" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B38" s="21" t="n"/>
       <c r="C38" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -43066,9 +40677,7 @@
           <t>EOG</t>
         </is>
       </c>
-      <c r="B39" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B39" s="21" t="n"/>
       <c r="C39" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -43120,9 +40729,7 @@
           <t>MDB</t>
         </is>
       </c>
-      <c r="B40" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B40" s="21" t="n"/>
       <c r="C40" s="5" t="inlineStr">
         <is>
           <t>11 AI软件 / SAAS</t>
@@ -43174,9 +40781,7 @@
           <t>OXY</t>
         </is>
       </c>
-      <c r="B41" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B41" s="21" t="n"/>
       <c r="C41" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -43228,9 +40833,7 @@
           <t>POET</t>
         </is>
       </c>
-      <c r="B42" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B42" s="21" t="n"/>
       <c r="C42" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -43282,9 +40885,7 @@
           <t>XLE</t>
         </is>
       </c>
-      <c r="B43" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B43" s="21" t="n"/>
       <c r="C43" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -43394,9 +40995,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -43408,7 +41006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -43631,7 +41229,7 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点</t>
+          <t>正式买入 | 第一观察点</t>
         </is>
       </c>
       <c r="F5" s="12" t="n">
@@ -43679,7 +41277,7 @@
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F6" s="12" t="n">
@@ -43837,7 +41435,6 @@
       <c r="F9" t="n">
         <v>190.96</v>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>203.7</v>
       </c>
@@ -43856,7 +41453,6 @@
       <c r="M9" s="11" t="n">
         <v>0.299487</v>
       </c>
-      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
@@ -43960,7 +41556,6 @@
       <c r="M11" s="20" t="n">
         <v>-0.04189</v>
       </c>
-      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
@@ -44238,9 +41833,7 @@
           <t>SLB</t>
         </is>
       </c>
-      <c r="B25" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B25" s="21" t="n"/>
       <c r="C25" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -44286,9 +41879,7 @@
           <t>ZS</t>
         </is>
       </c>
-      <c r="B26" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B26" s="21" t="n"/>
       <c r="C26" s="5" t="inlineStr">
         <is>
           <t>12 网络安全</t>
@@ -44379,10 +41970,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
